--- a/docs/詳細設計書/[共通仕様]詳細設計書_ログ仕様.xlsx
+++ b/docs/詳細設計書/[共通仕様]詳細設計書_ログ仕様.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19815" windowHeight="7575"/>
+    <workbookView windowWidth="19815" windowHeight="7575" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="改訂履歴" sheetId="11" r:id="rId1"/>
@@ -52,11 +52,11 @@
     <t>1.1</t>
   </si>
   <si>
-    <t>◆機能概要　修正
-概要の説明を、機能設計書から詳細設計書に変更
-◆ログ出力仕様　追記
-例外ログの出力仕様
-ログローテーションルール</t>
+    <t>◆機能概要
+　・概要の説明を、機能設計書から詳細設計書に変更
+◆ログ出力仕様に下記内容を追記
+　・例外ログの出力仕様
+　・ログローテーションルール</t>
   </si>
   <si>
     <t>機能概要</t>
@@ -117,6 +117,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <charset val="128"/>
+      </rPr>
       <t>出力される操作対象は各画面の</t>
     </r>
     <r>
@@ -489,12 +495,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="30">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -534,14 +540,7 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Meiryo UI"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color rgb="FF1F2328"/>
       <name val="Meiryo UI"/>
       <charset val="128"/>
@@ -554,13 +553,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Meiryo UI"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Meiryo UI"/>
       <charset val="128"/>
@@ -572,14 +565,38 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Meiryo UI"/>
-      <charset val="128"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -593,29 +610,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF0000FF"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -630,15 +641,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -652,24 +655,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -683,8 +684,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF7F7F7F"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -698,29 +700,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -728,8 +707,16 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="38">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -762,31 +749,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -804,19 +767,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -834,7 +821,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -846,7 +845,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -858,7 +857,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -870,55 +893,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -931,24 +918,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1120,6 +1089,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -1131,6 +1124,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1152,11 +1160,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1172,48 +1178,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1222,152 +1191,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="19" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1575,97 +1544,73 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1692,34 +1637,37 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
@@ -2474,520 +2422,520 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="106" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="112"/>
-      <c r="B2" s="114" t="s">
+      <c r="A2" s="106"/>
+      <c r="B2" s="108" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="115" t="s">
+      <c r="C2" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="115" t="s">
+      <c r="D2" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="115" t="s">
+      <c r="E2" s="82" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="112"/>
-      <c r="B3" s="116" t="s">
+      <c r="A3" s="106"/>
+      <c r="B3" s="109" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="117">
+      <c r="C3" s="110">
         <v>45636</v>
       </c>
-      <c r="D3" s="118" t="s">
+      <c r="D3" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="118" t="s">
+      <c r="E3" s="111" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" ht="91" customHeight="1" spans="1:5">
-      <c r="A4" s="112"/>
-      <c r="B4" s="116" t="s">
+      <c r="A4" s="106"/>
+      <c r="B4" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="117">
+      <c r="C4" s="110">
         <v>45735</v>
       </c>
-      <c r="D4" s="118" t="s">
+      <c r="D4" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="119" t="s">
+      <c r="E4" s="112" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="112"/>
-      <c r="B5" s="116"/>
-      <c r="C5" s="118"/>
-      <c r="D5" s="118"/>
-      <c r="E5" s="118"/>
+      <c r="A5" s="106"/>
+      <c r="B5" s="109"/>
+      <c r="C5" s="111"/>
+      <c r="D5" s="111"/>
+      <c r="E5" s="111"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="112"/>
-      <c r="B6" s="116"/>
-      <c r="C6" s="118"/>
-      <c r="D6" s="118"/>
-      <c r="E6" s="118"/>
+      <c r="A6" s="106"/>
+      <c r="B6" s="109"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="111"/>
+      <c r="E6" s="111"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="112"/>
-      <c r="B7" s="116"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118"/>
+      <c r="A7" s="106"/>
+      <c r="B7" s="109"/>
+      <c r="C7" s="111"/>
+      <c r="D7" s="111"/>
+      <c r="E7" s="111"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="112"/>
-      <c r="B8" s="116"/>
-      <c r="C8" s="118"/>
-      <c r="D8" s="118"/>
-      <c r="E8" s="118"/>
+      <c r="A8" s="106"/>
+      <c r="B8" s="109"/>
+      <c r="C8" s="111"/>
+      <c r="D8" s="111"/>
+      <c r="E8" s="111"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="112"/>
-      <c r="B9" s="116"/>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="118"/>
+      <c r="A9" s="106"/>
+      <c r="B9" s="109"/>
+      <c r="C9" s="111"/>
+      <c r="D9" s="111"/>
+      <c r="E9" s="111"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="112"/>
-      <c r="B10" s="116"/>
-      <c r="C10" s="118"/>
-      <c r="D10" s="118"/>
-      <c r="E10" s="118"/>
+      <c r="A10" s="106"/>
+      <c r="B10" s="109"/>
+      <c r="C10" s="111"/>
+      <c r="D10" s="111"/>
+      <c r="E10" s="111"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="112"/>
-      <c r="B11" s="116"/>
-      <c r="C11" s="118"/>
-      <c r="D11" s="118"/>
-      <c r="E11" s="118"/>
+      <c r="A11" s="106"/>
+      <c r="B11" s="109"/>
+      <c r="C11" s="111"/>
+      <c r="D11" s="111"/>
+      <c r="E11" s="111"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="112"/>
-      <c r="B12" s="116"/>
-      <c r="C12" s="118"/>
-      <c r="D12" s="118"/>
-      <c r="E12" s="118"/>
+      <c r="A12" s="106"/>
+      <c r="B12" s="109"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="111"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="112"/>
-      <c r="B13" s="116"/>
-      <c r="C13" s="118"/>
-      <c r="D13" s="118"/>
-      <c r="E13" s="118"/>
+      <c r="A13" s="106"/>
+      <c r="B13" s="109"/>
+      <c r="C13" s="111"/>
+      <c r="D13" s="111"/>
+      <c r="E13" s="111"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="112"/>
-      <c r="B14" s="116"/>
-      <c r="C14" s="118"/>
-      <c r="D14" s="118"/>
-      <c r="E14" s="118"/>
+      <c r="A14" s="106"/>
+      <c r="B14" s="109"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="111"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="112"/>
-      <c r="B15" s="116"/>
-      <c r="C15" s="118"/>
-      <c r="D15" s="118"/>
-      <c r="E15" s="118"/>
+      <c r="A15" s="106"/>
+      <c r="B15" s="109"/>
+      <c r="C15" s="111"/>
+      <c r="D15" s="111"/>
+      <c r="E15" s="111"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="112"/>
-      <c r="B16" s="116"/>
-      <c r="C16" s="118"/>
-      <c r="D16" s="118"/>
-      <c r="E16" s="118"/>
+      <c r="A16" s="106"/>
+      <c r="B16" s="109"/>
+      <c r="C16" s="111"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="111"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="112"/>
-      <c r="B17" s="116"/>
-      <c r="C17" s="118"/>
-      <c r="D17" s="118"/>
-      <c r="E17" s="118"/>
+      <c r="A17" s="106"/>
+      <c r="B17" s="109"/>
+      <c r="C17" s="111"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="111"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="112"/>
-      <c r="B18" s="116"/>
-      <c r="C18" s="118"/>
-      <c r="D18" s="118"/>
-      <c r="E18" s="118"/>
+      <c r="A18" s="106"/>
+      <c r="B18" s="109"/>
+      <c r="C18" s="111"/>
+      <c r="D18" s="111"/>
+      <c r="E18" s="111"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="112"/>
-      <c r="B19" s="116"/>
-      <c r="C19" s="118"/>
-      <c r="D19" s="118"/>
-      <c r="E19" s="118"/>
+      <c r="A19" s="106"/>
+      <c r="B19" s="109"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="111"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="112"/>
-      <c r="B20" s="116"/>
-      <c r="C20" s="118"/>
-      <c r="D20" s="118"/>
-      <c r="E20" s="118"/>
+      <c r="A20" s="106"/>
+      <c r="B20" s="109"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="111"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="112"/>
-      <c r="B21" s="116"/>
-      <c r="C21" s="118"/>
-      <c r="D21" s="118"/>
-      <c r="E21" s="118"/>
+      <c r="A21" s="106"/>
+      <c r="B21" s="109"/>
+      <c r="C21" s="111"/>
+      <c r="D21" s="111"/>
+      <c r="E21" s="111"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="112"/>
-      <c r="B22" s="116"/>
-      <c r="C22" s="118"/>
-      <c r="D22" s="118"/>
-      <c r="E22" s="118"/>
+      <c r="A22" s="106"/>
+      <c r="B22" s="109"/>
+      <c r="C22" s="111"/>
+      <c r="D22" s="111"/>
+      <c r="E22" s="111"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="112"/>
-      <c r="B23" s="116"/>
-      <c r="C23" s="118"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="118"/>
+      <c r="A23" s="106"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="111"/>
+      <c r="D23" s="111"/>
+      <c r="E23" s="111"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="112"/>
-      <c r="B24" s="116"/>
-      <c r="C24" s="118"/>
-      <c r="D24" s="118"/>
-      <c r="E24" s="118"/>
+      <c r="A24" s="106"/>
+      <c r="B24" s="109"/>
+      <c r="C24" s="111"/>
+      <c r="D24" s="111"/>
+      <c r="E24" s="111"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="112"/>
-      <c r="B25" s="116"/>
-      <c r="C25" s="118"/>
-      <c r="D25" s="118"/>
-      <c r="E25" s="118"/>
+      <c r="A25" s="106"/>
+      <c r="B25" s="109"/>
+      <c r="C25" s="111"/>
+      <c r="D25" s="111"/>
+      <c r="E25" s="111"/>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="112"/>
-      <c r="B26" s="116"/>
-      <c r="C26" s="118"/>
-      <c r="D26" s="118"/>
-      <c r="E26" s="118"/>
+      <c r="A26" s="106"/>
+      <c r="B26" s="109"/>
+      <c r="C26" s="111"/>
+      <c r="D26" s="111"/>
+      <c r="E26" s="111"/>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="112"/>
-      <c r="B27" s="116"/>
-      <c r="C27" s="118"/>
-      <c r="D27" s="118"/>
-      <c r="E27" s="118"/>
+      <c r="A27" s="106"/>
+      <c r="B27" s="109"/>
+      <c r="C27" s="111"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="111"/>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="112"/>
-      <c r="B28" s="116"/>
-      <c r="C28" s="118"/>
-      <c r="D28" s="118"/>
-      <c r="E28" s="118"/>
+      <c r="A28" s="106"/>
+      <c r="B28" s="109"/>
+      <c r="C28" s="111"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="111"/>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="112"/>
-      <c r="B29" s="116"/>
-      <c r="C29" s="118"/>
-      <c r="D29" s="118"/>
-      <c r="E29" s="118"/>
+      <c r="A29" s="106"/>
+      <c r="B29" s="109"/>
+      <c r="C29" s="111"/>
+      <c r="D29" s="111"/>
+      <c r="E29" s="111"/>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="112"/>
-      <c r="B30" s="116"/>
-      <c r="C30" s="118"/>
-      <c r="D30" s="118"/>
-      <c r="E30" s="118"/>
+      <c r="A30" s="106"/>
+      <c r="B30" s="109"/>
+      <c r="C30" s="111"/>
+      <c r="D30" s="111"/>
+      <c r="E30" s="111"/>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="112"/>
-      <c r="B31" s="116"/>
-      <c r="C31" s="118"/>
-      <c r="D31" s="118"/>
-      <c r="E31" s="118"/>
+      <c r="A31" s="106"/>
+      <c r="B31" s="109"/>
+      <c r="C31" s="111"/>
+      <c r="D31" s="111"/>
+      <c r="E31" s="111"/>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="112"/>
-      <c r="B32" s="116"/>
-      <c r="C32" s="118"/>
-      <c r="D32" s="118"/>
-      <c r="E32" s="118"/>
+      <c r="A32" s="106"/>
+      <c r="B32" s="109"/>
+      <c r="C32" s="111"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="111"/>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="112"/>
-      <c r="B33" s="116"/>
-      <c r="C33" s="118"/>
-      <c r="D33" s="118"/>
-      <c r="E33" s="118"/>
+      <c r="A33" s="106"/>
+      <c r="B33" s="109"/>
+      <c r="C33" s="111"/>
+      <c r="D33" s="111"/>
+      <c r="E33" s="111"/>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="112"/>
-      <c r="B34" s="116"/>
-      <c r="C34" s="118"/>
-      <c r="D34" s="118"/>
-      <c r="E34" s="118"/>
+      <c r="A34" s="106"/>
+      <c r="B34" s="109"/>
+      <c r="C34" s="111"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="111"/>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="112"/>
-      <c r="B35" s="116"/>
-      <c r="C35" s="118"/>
-      <c r="D35" s="118"/>
-      <c r="E35" s="118"/>
+      <c r="A35" s="106"/>
+      <c r="B35" s="109"/>
+      <c r="C35" s="111"/>
+      <c r="D35" s="111"/>
+      <c r="E35" s="111"/>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="112"/>
-      <c r="B36" s="116"/>
-      <c r="C36" s="118"/>
-      <c r="D36" s="118"/>
-      <c r="E36" s="118"/>
+      <c r="A36" s="106"/>
+      <c r="B36" s="109"/>
+      <c r="C36" s="111"/>
+      <c r="D36" s="111"/>
+      <c r="E36" s="111"/>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="112"/>
-      <c r="B37" s="116"/>
-      <c r="C37" s="118"/>
-      <c r="D37" s="118"/>
-      <c r="E37" s="118"/>
+      <c r="A37" s="106"/>
+      <c r="B37" s="109"/>
+      <c r="C37" s="111"/>
+      <c r="D37" s="111"/>
+      <c r="E37" s="111"/>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="112"/>
-      <c r="B38" s="116"/>
-      <c r="C38" s="118"/>
-      <c r="D38" s="118"/>
-      <c r="E38" s="118"/>
+      <c r="A38" s="106"/>
+      <c r="B38" s="109"/>
+      <c r="C38" s="111"/>
+      <c r="D38" s="111"/>
+      <c r="E38" s="111"/>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="112"/>
-      <c r="B39" s="116"/>
-      <c r="C39" s="118"/>
-      <c r="D39" s="118"/>
-      <c r="E39" s="118"/>
+      <c r="A39" s="106"/>
+      <c r="B39" s="109"/>
+      <c r="C39" s="111"/>
+      <c r="D39" s="111"/>
+      <c r="E39" s="111"/>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="112"/>
-      <c r="B40" s="116"/>
-      <c r="C40" s="118"/>
-      <c r="D40" s="118"/>
-      <c r="E40" s="118"/>
+      <c r="A40" s="106"/>
+      <c r="B40" s="109"/>
+      <c r="C40" s="111"/>
+      <c r="D40" s="111"/>
+      <c r="E40" s="111"/>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="112"/>
-      <c r="B41" s="116"/>
-      <c r="C41" s="118"/>
-      <c r="D41" s="118"/>
-      <c r="E41" s="118"/>
+      <c r="A41" s="106"/>
+      <c r="B41" s="109"/>
+      <c r="C41" s="111"/>
+      <c r="D41" s="111"/>
+      <c r="E41" s="111"/>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="112"/>
-      <c r="B42" s="116"/>
-      <c r="C42" s="118"/>
-      <c r="D42" s="118"/>
-      <c r="E42" s="118"/>
+      <c r="A42" s="106"/>
+      <c r="B42" s="109"/>
+      <c r="C42" s="111"/>
+      <c r="D42" s="111"/>
+      <c r="E42" s="111"/>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="112"/>
-      <c r="B43" s="116"/>
-      <c r="C43" s="118"/>
-      <c r="D43" s="118"/>
-      <c r="E43" s="118"/>
+      <c r="A43" s="106"/>
+      <c r="B43" s="109"/>
+      <c r="C43" s="111"/>
+      <c r="D43" s="111"/>
+      <c r="E43" s="111"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="112"/>
-      <c r="B44" s="116"/>
-      <c r="C44" s="118"/>
-      <c r="D44" s="118"/>
-      <c r="E44" s="118"/>
+      <c r="A44" s="106"/>
+      <c r="B44" s="109"/>
+      <c r="C44" s="111"/>
+      <c r="D44" s="111"/>
+      <c r="E44" s="111"/>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="112"/>
-      <c r="B45" s="116"/>
-      <c r="C45" s="118"/>
-      <c r="D45" s="118"/>
-      <c r="E45" s="118"/>
+      <c r="A45" s="106"/>
+      <c r="B45" s="109"/>
+      <c r="C45" s="111"/>
+      <c r="D45" s="111"/>
+      <c r="E45" s="111"/>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="112"/>
-      <c r="B46" s="116"/>
-      <c r="C46" s="118"/>
-      <c r="D46" s="118"/>
-      <c r="E46" s="118"/>
+      <c r="A46" s="106"/>
+      <c r="B46" s="109"/>
+      <c r="C46" s="111"/>
+      <c r="D46" s="111"/>
+      <c r="E46" s="111"/>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="112"/>
-      <c r="B47" s="116"/>
-      <c r="C47" s="118"/>
-      <c r="D47" s="118"/>
-      <c r="E47" s="118"/>
+      <c r="A47" s="106"/>
+      <c r="B47" s="109"/>
+      <c r="C47" s="111"/>
+      <c r="D47" s="111"/>
+      <c r="E47" s="111"/>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="112"/>
-      <c r="B48" s="116"/>
-      <c r="C48" s="118"/>
-      <c r="D48" s="118"/>
-      <c r="E48" s="118"/>
+      <c r="A48" s="106"/>
+      <c r="B48" s="109"/>
+      <c r="C48" s="111"/>
+      <c r="D48" s="111"/>
+      <c r="E48" s="111"/>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="112"/>
-      <c r="B49" s="116"/>
-      <c r="C49" s="118"/>
-      <c r="D49" s="118"/>
-      <c r="E49" s="118"/>
+      <c r="A49" s="106"/>
+      <c r="B49" s="109"/>
+      <c r="C49" s="111"/>
+      <c r="D49" s="111"/>
+      <c r="E49" s="111"/>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="112"/>
-      <c r="B50" s="116"/>
-      <c r="C50" s="118"/>
-      <c r="D50" s="118"/>
-      <c r="E50" s="118"/>
+      <c r="A50" s="106"/>
+      <c r="B50" s="109"/>
+      <c r="C50" s="111"/>
+      <c r="D50" s="111"/>
+      <c r="E50" s="111"/>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="112"/>
-      <c r="B51" s="116"/>
-      <c r="C51" s="118"/>
-      <c r="D51" s="118"/>
-      <c r="E51" s="118"/>
+      <c r="A51" s="106"/>
+      <c r="B51" s="109"/>
+      <c r="C51" s="111"/>
+      <c r="D51" s="111"/>
+      <c r="E51" s="111"/>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="112"/>
-      <c r="B52" s="116"/>
-      <c r="C52" s="118"/>
-      <c r="D52" s="118"/>
-      <c r="E52" s="118"/>
+      <c r="A52" s="106"/>
+      <c r="B52" s="109"/>
+      <c r="C52" s="111"/>
+      <c r="D52" s="111"/>
+      <c r="E52" s="111"/>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="112"/>
-      <c r="B53" s="116"/>
-      <c r="C53" s="118"/>
-      <c r="D53" s="118"/>
-      <c r="E53" s="118"/>
+      <c r="A53" s="106"/>
+      <c r="B53" s="109"/>
+      <c r="C53" s="111"/>
+      <c r="D53" s="111"/>
+      <c r="E53" s="111"/>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="112"/>
-      <c r="B54" s="116"/>
-      <c r="C54" s="118"/>
-      <c r="D54" s="118"/>
-      <c r="E54" s="118"/>
+      <c r="A54" s="106"/>
+      <c r="B54" s="109"/>
+      <c r="C54" s="111"/>
+      <c r="D54" s="111"/>
+      <c r="E54" s="111"/>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="112"/>
-      <c r="B55" s="116"/>
-      <c r="C55" s="118"/>
-      <c r="D55" s="118"/>
-      <c r="E55" s="118"/>
+      <c r="A55" s="106"/>
+      <c r="B55" s="109"/>
+      <c r="C55" s="111"/>
+      <c r="D55" s="111"/>
+      <c r="E55" s="111"/>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="112"/>
-      <c r="B56" s="116"/>
-      <c r="C56" s="118"/>
-      <c r="D56" s="118"/>
-      <c r="E56" s="118"/>
+      <c r="A56" s="106"/>
+      <c r="B56" s="109"/>
+      <c r="C56" s="111"/>
+      <c r="D56" s="111"/>
+      <c r="E56" s="111"/>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="112"/>
-      <c r="B57" s="116"/>
-      <c r="C57" s="118"/>
-      <c r="D57" s="118"/>
-      <c r="E57" s="118"/>
+      <c r="A57" s="106"/>
+      <c r="B57" s="109"/>
+      <c r="C57" s="111"/>
+      <c r="D57" s="111"/>
+      <c r="E57" s="111"/>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="112"/>
-      <c r="B58" s="116"/>
-      <c r="C58" s="118"/>
-      <c r="D58" s="118"/>
-      <c r="E58" s="118"/>
+      <c r="A58" s="106"/>
+      <c r="B58" s="109"/>
+      <c r="C58" s="111"/>
+      <c r="D58" s="111"/>
+      <c r="E58" s="111"/>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="112"/>
-      <c r="B59" s="116"/>
-      <c r="C59" s="118"/>
-      <c r="D59" s="118"/>
-      <c r="E59" s="118"/>
+      <c r="A59" s="106"/>
+      <c r="B59" s="109"/>
+      <c r="C59" s="111"/>
+      <c r="D59" s="111"/>
+      <c r="E59" s="111"/>
     </row>
     <row r="60" spans="1:5">
-      <c r="A60" s="112"/>
-      <c r="B60" s="116"/>
-      <c r="C60" s="118"/>
-      <c r="D60" s="118"/>
-      <c r="E60" s="118"/>
+      <c r="A60" s="106"/>
+      <c r="B60" s="109"/>
+      <c r="C60" s="111"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="112"/>
-      <c r="B61" s="116"/>
-      <c r="C61" s="118"/>
-      <c r="D61" s="118"/>
-      <c r="E61" s="118"/>
+      <c r="A61" s="106"/>
+      <c r="B61" s="109"/>
+      <c r="C61" s="111"/>
+      <c r="D61" s="111"/>
+      <c r="E61" s="111"/>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="112"/>
-      <c r="B62" s="116"/>
-      <c r="C62" s="118"/>
-      <c r="D62" s="118"/>
-      <c r="E62" s="118"/>
+      <c r="A62" s="106"/>
+      <c r="B62" s="109"/>
+      <c r="C62" s="111"/>
+      <c r="D62" s="111"/>
+      <c r="E62" s="111"/>
     </row>
     <row r="63" spans="1:5">
-      <c r="A63" s="112"/>
-      <c r="B63" s="116"/>
-      <c r="C63" s="118"/>
-      <c r="D63" s="118"/>
-      <c r="E63" s="118"/>
+      <c r="A63" s="106"/>
+      <c r="B63" s="109"/>
+      <c r="C63" s="111"/>
+      <c r="D63" s="111"/>
+      <c r="E63" s="111"/>
     </row>
     <row r="64" spans="1:5">
-      <c r="A64" s="112"/>
-      <c r="B64" s="116"/>
-      <c r="C64" s="118"/>
-      <c r="D64" s="118"/>
-      <c r="E64" s="118"/>
+      <c r="A64" s="106"/>
+      <c r="B64" s="109"/>
+      <c r="C64" s="111"/>
+      <c r="D64" s="111"/>
+      <c r="E64" s="111"/>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="112"/>
-      <c r="B65" s="116"/>
-      <c r="C65" s="118"/>
-      <c r="D65" s="118"/>
-      <c r="E65" s="118"/>
+      <c r="A65" s="106"/>
+      <c r="B65" s="109"/>
+      <c r="C65" s="111"/>
+      <c r="D65" s="111"/>
+      <c r="E65" s="111"/>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="112"/>
-      <c r="B66" s="116"/>
-      <c r="C66" s="118"/>
-      <c r="D66" s="118"/>
-      <c r="E66" s="118"/>
+      <c r="A66" s="106"/>
+      <c r="B66" s="109"/>
+      <c r="C66" s="111"/>
+      <c r="D66" s="111"/>
+      <c r="E66" s="111"/>
     </row>
     <row r="67" spans="1:5">
-      <c r="A67" s="112"/>
-      <c r="B67" s="116"/>
-      <c r="C67" s="118"/>
-      <c r="D67" s="118"/>
-      <c r="E67" s="118"/>
+      <c r="A67" s="106"/>
+      <c r="B67" s="109"/>
+      <c r="C67" s="111"/>
+      <c r="D67" s="111"/>
+      <c r="E67" s="111"/>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="112"/>
-      <c r="B68" s="116"/>
-      <c r="C68" s="118"/>
-      <c r="D68" s="118"/>
-      <c r="E68" s="118"/>
+      <c r="A68" s="106"/>
+      <c r="B68" s="109"/>
+      <c r="C68" s="111"/>
+      <c r="D68" s="111"/>
+      <c r="E68" s="111"/>
     </row>
     <row r="69" spans="1:5">
-      <c r="A69" s="112"/>
-      <c r="B69" s="113"/>
-      <c r="C69" s="112"/>
-      <c r="D69" s="112"/>
-      <c r="E69" s="112"/>
+      <c r="A69" s="106"/>
+      <c r="B69" s="107"/>
+      <c r="C69" s="106"/>
+      <c r="D69" s="106"/>
+      <c r="E69" s="106"/>
     </row>
     <row r="70" spans="1:5">
-      <c r="A70" s="112"/>
-      <c r="B70" s="113"/>
-      <c r="C70" s="112"/>
-      <c r="D70" s="112"/>
-      <c r="E70" s="112"/>
+      <c r="A70" s="106"/>
+      <c r="B70" s="107"/>
+      <c r="C70" s="106"/>
+      <c r="D70" s="106"/>
+      <c r="E70" s="106"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3021,40 +2969,40 @@
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
       <c r="N1" s="18"/>
-      <c r="O1" s="85" t="s">
+      <c r="O1" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="85"/>
-      <c r="Q1" s="85"/>
-      <c r="R1" s="85"/>
-      <c r="S1" s="85"/>
-      <c r="T1" s="98" t="s">
+      <c r="P1" s="82"/>
+      <c r="Q1" s="82"/>
+      <c r="R1" s="82"/>
+      <c r="S1" s="82"/>
+      <c r="T1" s="91" t="s">
         <v>12</v>
       </c>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="101"/>
-      <c r="AB1" s="85" t="s">
+      <c r="U1" s="92"/>
+      <c r="V1" s="92"/>
+      <c r="W1" s="92"/>
+      <c r="X1" s="92"/>
+      <c r="Y1" s="92"/>
+      <c r="Z1" s="92"/>
+      <c r="AA1" s="93"/>
+      <c r="AB1" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="AC1" s="85"/>
-      <c r="AD1" s="85"/>
-      <c r="AE1" s="111" t="s">
+      <c r="AC1" s="82"/>
+      <c r="AD1" s="82"/>
+      <c r="AE1" s="105" t="s">
         <v>6</v>
       </c>
       <c r="AF1" s="19"/>
       <c r="AG1" s="19"/>
       <c r="AH1" s="19"/>
-      <c r="AI1" s="85" t="s">
+      <c r="AI1" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="AJ1" s="85"/>
-      <c r="AK1" s="85"/>
-      <c r="AL1" s="120" t="s">
+      <c r="AJ1" s="82"/>
+      <c r="AK1" s="82"/>
+      <c r="AL1" s="113" t="s">
         <v>14</v>
       </c>
       <c r="AM1" s="19"/>
@@ -3076,33 +3024,33 @@
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="20"/>
-      <c r="O2" s="85" t="s">
+      <c r="O2" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="85"/>
-      <c r="Q2" s="85"/>
-      <c r="R2" s="85"/>
-      <c r="S2" s="85"/>
-      <c r="T2" s="98" t="s">
+      <c r="P2" s="82"/>
+      <c r="Q2" s="82"/>
+      <c r="R2" s="82"/>
+      <c r="S2" s="82"/>
+      <c r="T2" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="U2" s="99"/>
-      <c r="V2" s="99"/>
-      <c r="W2" s="99"/>
-      <c r="X2" s="99"/>
-      <c r="Y2" s="99"/>
-      <c r="Z2" s="99"/>
-      <c r="AA2" s="101"/>
-      <c r="AB2" s="85"/>
-      <c r="AC2" s="85"/>
-      <c r="AD2" s="85"/>
+      <c r="U2" s="92"/>
+      <c r="V2" s="92"/>
+      <c r="W2" s="92"/>
+      <c r="X2" s="92"/>
+      <c r="Y2" s="92"/>
+      <c r="Z2" s="92"/>
+      <c r="AA2" s="93"/>
+      <c r="AB2" s="82"/>
+      <c r="AC2" s="82"/>
+      <c r="AD2" s="82"/>
       <c r="AE2" s="19"/>
       <c r="AF2" s="19"/>
       <c r="AG2" s="19"/>
       <c r="AH2" s="19"/>
-      <c r="AI2" s="85"/>
-      <c r="AJ2" s="85"/>
-      <c r="AK2" s="85"/>
+      <c r="AI2" s="82"/>
+      <c r="AJ2" s="82"/>
+      <c r="AK2" s="82"/>
       <c r="AL2" s="19"/>
       <c r="AM2" s="19"/>
       <c r="AN2" s="19"/>
@@ -3123,13 +3071,13 @@
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
       <c r="N3" s="20"/>
-      <c r="O3" s="85" t="s">
+      <c r="O3" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="85"/>
-      <c r="Q3" s="85"/>
-      <c r="R3" s="85"/>
-      <c r="S3" s="85"/>
+      <c r="P3" s="82"/>
+      <c r="Q3" s="82"/>
+      <c r="R3" s="82"/>
+      <c r="S3" s="82"/>
       <c r="T3" s="19" t="s">
         <v>18</v>
       </c>
@@ -3140,23 +3088,23 @@
       <c r="Y3" s="19"/>
       <c r="Z3" s="19"/>
       <c r="AA3" s="19"/>
-      <c r="AB3" s="85" t="s">
+      <c r="AB3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="AC3" s="85"/>
-      <c r="AD3" s="85"/>
-      <c r="AE3" s="111" t="s">
+      <c r="AC3" s="82"/>
+      <c r="AD3" s="82"/>
+      <c r="AE3" s="105" t="s">
         <v>6</v>
       </c>
       <c r="AF3" s="19"/>
       <c r="AG3" s="19"/>
       <c r="AH3" s="19"/>
-      <c r="AI3" s="85" t="s">
+      <c r="AI3" s="82" t="s">
         <v>20</v>
       </c>
-      <c r="AJ3" s="85"/>
-      <c r="AK3" s="85"/>
-      <c r="AL3" s="111">
+      <c r="AJ3" s="82"/>
+      <c r="AK3" s="82"/>
+      <c r="AL3" s="105">
         <v>45735</v>
       </c>
       <c r="AM3" s="19"/>
@@ -3178,13 +3126,13 @@
       <c r="L4" s="30"/>
       <c r="M4" s="30"/>
       <c r="N4" s="34"/>
-      <c r="O4" s="85" t="s">
+      <c r="O4" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="P4" s="85"/>
-      <c r="Q4" s="85"/>
-      <c r="R4" s="85"/>
-      <c r="S4" s="85"/>
+      <c r="P4" s="82"/>
+      <c r="Q4" s="82"/>
+      <c r="R4" s="82"/>
+      <c r="S4" s="82"/>
       <c r="T4" s="19" t="s">
         <v>22</v>
       </c>
@@ -3195,69 +3143,69 @@
       <c r="Y4" s="19"/>
       <c r="Z4" s="19"/>
       <c r="AA4" s="19"/>
-      <c r="AB4" s="85"/>
-      <c r="AC4" s="85"/>
-      <c r="AD4" s="85"/>
+      <c r="AB4" s="82"/>
+      <c r="AC4" s="82"/>
+      <c r="AD4" s="82"/>
       <c r="AE4" s="19"/>
       <c r="AF4" s="19"/>
       <c r="AG4" s="19"/>
       <c r="AH4" s="19"/>
-      <c r="AI4" s="85"/>
-      <c r="AJ4" s="85"/>
-      <c r="AK4" s="85"/>
+      <c r="AI4" s="82"/>
+      <c r="AJ4" s="82"/>
+      <c r="AK4" s="82"/>
       <c r="AL4" s="19"/>
       <c r="AM4" s="19"/>
       <c r="AN4" s="19"/>
       <c r="AO4" s="19"/>
     </row>
     <row r="5" customHeight="1" spans="1:41">
-      <c r="A5" s="107" t="s">
+      <c r="A5" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="107"/>
-      <c r="C5" s="107"/>
-      <c r="D5" s="107"/>
-      <c r="E5" s="107"/>
-      <c r="F5" s="107"/>
-      <c r="G5" s="107"/>
-      <c r="H5" s="107"/>
-      <c r="I5" s="107"/>
-      <c r="J5" s="107"/>
-      <c r="K5" s="107"/>
-      <c r="L5" s="107"/>
-      <c r="M5" s="107"/>
-      <c r="N5" s="107"/>
-      <c r="O5" s="107"/>
-      <c r="P5" s="107"/>
-      <c r="Q5" s="107"/>
-      <c r="R5" s="107"/>
-      <c r="S5" s="107"/>
-      <c r="T5" s="107"/>
-      <c r="U5" s="107"/>
-      <c r="V5" s="107"/>
-      <c r="W5" s="107" t="s">
+      <c r="B5" s="99"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="99"/>
+      <c r="F5" s="99"/>
+      <c r="G5" s="99"/>
+      <c r="H5" s="99"/>
+      <c r="I5" s="99"/>
+      <c r="J5" s="99"/>
+      <c r="K5" s="99"/>
+      <c r="L5" s="99"/>
+      <c r="M5" s="99"/>
+      <c r="N5" s="99"/>
+      <c r="O5" s="99"/>
+      <c r="P5" s="99"/>
+      <c r="Q5" s="99"/>
+      <c r="R5" s="99"/>
+      <c r="S5" s="99"/>
+      <c r="T5" s="99"/>
+      <c r="U5" s="99"/>
+      <c r="V5" s="99"/>
+      <c r="W5" s="99" t="s">
         <v>10</v>
       </c>
-      <c r="X5" s="107"/>
-      <c r="Y5" s="107"/>
-      <c r="Z5" s="107"/>
-      <c r="AA5" s="107"/>
-      <c r="AB5" s="107"/>
-      <c r="AC5" s="107"/>
-      <c r="AD5" s="107"/>
-      <c r="AE5" s="107"/>
-      <c r="AF5" s="107"/>
-      <c r="AG5" s="107"/>
-      <c r="AH5" s="107"/>
-      <c r="AI5" s="107"/>
-      <c r="AJ5" s="107"/>
-      <c r="AK5" s="107"/>
-      <c r="AL5" s="107"/>
-      <c r="AM5" s="107" t="s">
+      <c r="X5" s="99"/>
+      <c r="Y5" s="99"/>
+      <c r="Z5" s="99"/>
+      <c r="AA5" s="99"/>
+      <c r="AB5" s="99"/>
+      <c r="AC5" s="99"/>
+      <c r="AD5" s="99"/>
+      <c r="AE5" s="99"/>
+      <c r="AF5" s="99"/>
+      <c r="AG5" s="99"/>
+      <c r="AH5" s="99"/>
+      <c r="AI5" s="99"/>
+      <c r="AJ5" s="99"/>
+      <c r="AK5" s="99"/>
+      <c r="AL5" s="99"/>
+      <c r="AM5" s="99" t="s">
         <v>24</v>
       </c>
-      <c r="AN5" s="107"/>
-      <c r="AO5" s="107"/>
+      <c r="AN5" s="99"/>
+      <c r="AO5" s="99"/>
     </row>
     <row r="6" customHeight="1" spans="1:41">
       <c r="A6" s="11"/>
@@ -3282,24 +3230,24 @@
       <c r="T6" s="12"/>
       <c r="U6" s="12"/>
       <c r="V6" s="26"/>
-      <c r="W6" s="38" t="s">
+      <c r="W6" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="X6" s="25"/>
-      <c r="Y6" s="25"/>
-      <c r="Z6" s="25"/>
+      <c r="X6" s="103"/>
+      <c r="Y6" s="103"/>
+      <c r="Z6" s="103"/>
       <c r="AA6" s="19" t="s">
         <v>26</v>
       </c>
       <c r="AB6" s="19"/>
       <c r="AC6" s="19"/>
       <c r="AD6" s="19"/>
-      <c r="AE6" s="25" t="s">
+      <c r="AE6" s="103" t="s">
         <v>27</v>
       </c>
-      <c r="AF6" s="25"/>
-      <c r="AG6" s="25"/>
-      <c r="AH6" s="25"/>
+      <c r="AF6" s="103"/>
+      <c r="AG6" s="103"/>
+      <c r="AH6" s="103"/>
       <c r="AI6" s="19" t="s">
         <v>26</v>
       </c>
@@ -3626,63 +3574,63 @@
       <c r="AO19" s="28"/>
     </row>
     <row r="20" customHeight="1" spans="1:41">
-      <c r="A20" s="107" t="s">
+      <c r="A20" s="99" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="107"/>
-      <c r="C20" s="107" t="s">
+      <c r="B20" s="99"/>
+      <c r="C20" s="99" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="107"/>
-      <c r="E20" s="107"/>
-      <c r="F20" s="107"/>
-      <c r="G20" s="107"/>
-      <c r="H20" s="107"/>
-      <c r="I20" s="107"/>
-      <c r="J20" s="107" t="s">
+      <c r="D20" s="99"/>
+      <c r="E20" s="99"/>
+      <c r="F20" s="99"/>
+      <c r="G20" s="99"/>
+      <c r="H20" s="99"/>
+      <c r="I20" s="99"/>
+      <c r="J20" s="99" t="s">
         <v>33</v>
       </c>
-      <c r="K20" s="107"/>
-      <c r="L20" s="107" t="s">
+      <c r="K20" s="99"/>
+      <c r="L20" s="99" t="s">
         <v>34</v>
       </c>
-      <c r="M20" s="107" t="s">
+      <c r="M20" s="99" t="s">
         <v>35</v>
       </c>
-      <c r="N20" s="107" t="s">
+      <c r="N20" s="99" t="s">
         <v>36</v>
       </c>
-      <c r="O20" s="107" t="s">
+      <c r="O20" s="99" t="s">
         <v>37</v>
       </c>
-      <c r="P20" s="109" t="s">
+      <c r="P20" s="101" t="s">
         <v>38</v>
       </c>
-      <c r="Q20" s="110"/>
-      <c r="R20" s="110"/>
-      <c r="S20" s="110"/>
-      <c r="T20" s="110"/>
-      <c r="U20" s="110"/>
-      <c r="V20" s="110"/>
-      <c r="W20" s="110"/>
-      <c r="X20" s="110"/>
-      <c r="Y20" s="110"/>
-      <c r="Z20" s="110"/>
-      <c r="AA20" s="110"/>
-      <c r="AB20" s="110"/>
-      <c r="AC20" s="110"/>
-      <c r="AD20" s="110"/>
-      <c r="AE20" s="110"/>
-      <c r="AF20" s="110"/>
-      <c r="AG20" s="110"/>
-      <c r="AH20" s="110"/>
-      <c r="AI20" s="110"/>
-      <c r="AJ20" s="110"/>
-      <c r="AK20" s="110"/>
-      <c r="AL20" s="110"/>
-      <c r="AM20" s="110"/>
-      <c r="AN20" s="110"/>
-      <c r="AO20" s="110"/>
+      <c r="Q20" s="104"/>
+      <c r="R20" s="104"/>
+      <c r="S20" s="104"/>
+      <c r="T20" s="104"/>
+      <c r="U20" s="104"/>
+      <c r="V20" s="104"/>
+      <c r="W20" s="104"/>
+      <c r="X20" s="104"/>
+      <c r="Y20" s="104"/>
+      <c r="Z20" s="104"/>
+      <c r="AA20" s="104"/>
+      <c r="AB20" s="104"/>
+      <c r="AC20" s="104"/>
+      <c r="AD20" s="104"/>
+      <c r="AE20" s="104"/>
+      <c r="AF20" s="104"/>
+      <c r="AG20" s="104"/>
+      <c r="AH20" s="104"/>
+      <c r="AI20" s="104"/>
+      <c r="AJ20" s="104"/>
+      <c r="AK20" s="104"/>
+      <c r="AL20" s="104"/>
+      <c r="AM20" s="104"/>
+      <c r="AN20" s="104"/>
+      <c r="AO20" s="104"/>
     </row>
     <row r="21" customHeight="1" spans="1:41">
       <c r="A21" s="19">
@@ -4121,8 +4069,8 @@
       <c r="AO30" s="57"/>
     </row>
     <row r="31" customHeight="1" spans="1:41">
-      <c r="A31" s="108"/>
-      <c r="B31" s="108"/>
+      <c r="A31" s="100"/>
+      <c r="B31" s="100"/>
       <c r="C31" s="61"/>
       <c r="D31" s="61"/>
       <c r="E31" s="61"/>
@@ -4245,7 +4193,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE55"/>
+  <dimension ref="A1:AE59"/>
   <sheetFormatPr defaultColWidth="3.66666666666667" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="3.66666666666667" style="1"/>
@@ -4282,33 +4230,33 @@
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
       <c r="N1" s="18"/>
-      <c r="O1" s="85" t="s">
+      <c r="O1" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="85"/>
-      <c r="Q1" s="85"/>
-      <c r="R1" s="85"/>
-      <c r="S1" s="85"/>
-      <c r="T1" s="98" t="s">
+      <c r="P1" s="82"/>
+      <c r="Q1" s="82"/>
+      <c r="R1" s="82"/>
+      <c r="S1" s="82"/>
+      <c r="T1" s="91" t="s">
         <v>12</v>
       </c>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="101"/>
-      <c r="AB1" s="102" t="s">
+      <c r="U1" s="92"/>
+      <c r="V1" s="92"/>
+      <c r="W1" s="92"/>
+      <c r="X1" s="92"/>
+      <c r="Y1" s="92"/>
+      <c r="Z1" s="92"/>
+      <c r="AA1" s="93"/>
+      <c r="AB1" s="94" t="s">
         <v>3</v>
       </c>
-      <c r="AC1" s="103" t="s">
+      <c r="AC1" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="AD1" s="102" t="s">
+      <c r="AD1" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="AE1" s="121" t="s">
+      <c r="AE1" s="114" t="s">
         <v>14</v>
       </c>
     </row>
@@ -4327,27 +4275,27 @@
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="20"/>
-      <c r="O2" s="85" t="s">
+      <c r="O2" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="85"/>
-      <c r="Q2" s="85"/>
-      <c r="R2" s="85"/>
-      <c r="S2" s="85"/>
-      <c r="T2" s="98" t="s">
+      <c r="P2" s="82"/>
+      <c r="Q2" s="82"/>
+      <c r="R2" s="82"/>
+      <c r="S2" s="82"/>
+      <c r="T2" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="U2" s="99"/>
-      <c r="V2" s="99"/>
-      <c r="W2" s="99"/>
-      <c r="X2" s="99"/>
-      <c r="Y2" s="99"/>
-      <c r="Z2" s="99"/>
-      <c r="AA2" s="101"/>
-      <c r="AB2" s="104"/>
-      <c r="AC2" s="105"/>
-      <c r="AD2" s="104"/>
-      <c r="AE2" s="105"/>
+      <c r="U2" s="92"/>
+      <c r="V2" s="92"/>
+      <c r="W2" s="92"/>
+      <c r="X2" s="92"/>
+      <c r="Y2" s="92"/>
+      <c r="Z2" s="92"/>
+      <c r="AA2" s="93"/>
+      <c r="AB2" s="96"/>
+      <c r="AC2" s="97"/>
+      <c r="AD2" s="96"/>
+      <c r="AE2" s="97"/>
     </row>
     <row r="3" customHeight="1" spans="1:31">
       <c r="A3" s="4"/>
@@ -4364,13 +4312,13 @@
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
       <c r="N3" s="20"/>
-      <c r="O3" s="85" t="s">
+      <c r="O3" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="85"/>
-      <c r="Q3" s="85"/>
-      <c r="R3" s="85"/>
-      <c r="S3" s="85"/>
+      <c r="P3" s="82"/>
+      <c r="Q3" s="82"/>
+      <c r="R3" s="82"/>
+      <c r="S3" s="82"/>
       <c r="T3" s="19" t="s">
         <v>18</v>
       </c>
@@ -4381,16 +4329,16 @@
       <c r="Y3" s="19"/>
       <c r="Z3" s="19"/>
       <c r="AA3" s="19"/>
-      <c r="AB3" s="102" t="s">
+      <c r="AB3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="AC3" s="103" t="s">
+      <c r="AC3" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="AD3" s="102" t="s">
+      <c r="AD3" s="94" t="s">
         <v>20</v>
       </c>
-      <c r="AE3" s="103">
+      <c r="AE3" s="95">
         <v>45735</v>
       </c>
     </row>
@@ -4409,13 +4357,13 @@
       <c r="L4" s="30"/>
       <c r="M4" s="30"/>
       <c r="N4" s="34"/>
-      <c r="O4" s="85" t="s">
+      <c r="O4" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="P4" s="85"/>
-      <c r="Q4" s="85"/>
-      <c r="R4" s="85"/>
-      <c r="S4" s="85"/>
+      <c r="P4" s="82"/>
+      <c r="Q4" s="82"/>
+      <c r="R4" s="82"/>
+      <c r="S4" s="82"/>
       <c r="T4" s="19" t="s">
         <v>22</v>
       </c>
@@ -4426,10 +4374,10 @@
       <c r="Y4" s="19"/>
       <c r="Z4" s="19"/>
       <c r="AA4" s="19"/>
-      <c r="AB4" s="104"/>
-      <c r="AC4" s="105"/>
-      <c r="AD4" s="104"/>
-      <c r="AE4" s="105"/>
+      <c r="AB4" s="96"/>
+      <c r="AC4" s="97"/>
+      <c r="AD4" s="96"/>
+      <c r="AE4" s="97"/>
     </row>
     <row r="5" customHeight="1" spans="1:31">
       <c r="A5" s="67" t="s">
@@ -4464,283 +4412,1051 @@
       <c r="AB5" s="68"/>
       <c r="AC5" s="68"/>
       <c r="AD5" s="68"/>
-      <c r="AE5" s="106"/>
+      <c r="AE5" s="98"/>
     </row>
     <row r="6" customHeight="1" spans="1:31">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12"/>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12"/>
-      <c r="S6" s="12"/>
-      <c r="T6" s="12"/>
-      <c r="U6" s="12"/>
-      <c r="V6" s="12"/>
-      <c r="W6" s="12"/>
-      <c r="X6" s="12"/>
-      <c r="Y6" s="12"/>
-      <c r="Z6" s="12"/>
-      <c r="AA6" s="12"/>
-      <c r="AB6" s="12"/>
-      <c r="AC6" s="12"/>
-      <c r="AD6" s="12"/>
-      <c r="AE6" s="12"/>
-    </row>
-    <row r="7" customHeight="1" spans="1:4">
-      <c r="A7" s="13"/>
-      <c r="B7" s="69" t="s">
+      <c r="A6" s="58"/>
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
+      <c r="L6" s="59"/>
+      <c r="M6" s="59"/>
+      <c r="N6" s="59"/>
+      <c r="O6" s="59"/>
+      <c r="P6" s="59"/>
+      <c r="Q6" s="59"/>
+      <c r="R6" s="59"/>
+      <c r="S6" s="59"/>
+      <c r="T6" s="59"/>
+      <c r="U6" s="59"/>
+      <c r="V6" s="59"/>
+      <c r="W6" s="59"/>
+      <c r="X6" s="59"/>
+      <c r="Y6" s="59"/>
+      <c r="Z6" s="59"/>
+      <c r="AA6" s="59"/>
+      <c r="AB6" s="59"/>
+      <c r="AC6" s="59"/>
+      <c r="AD6" s="59"/>
+      <c r="AE6" s="59"/>
+    </row>
+    <row r="7" customHeight="1" spans="1:31">
+      <c r="A7" s="60"/>
+      <c r="B7" s="15" t="s">
         <v>43</v>
       </c>
       <c r="C7" s="61"/>
       <c r="D7" s="61"/>
-    </row>
-    <row r="8" customHeight="1" spans="1:4">
-      <c r="A8" s="13"/>
-      <c r="B8" s="69"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="61"/>
+      <c r="L7" s="61"/>
+      <c r="M7" s="61"/>
+      <c r="N7" s="61"/>
+      <c r="O7" s="61"/>
+      <c r="P7" s="61"/>
+      <c r="Q7" s="61"/>
+      <c r="R7" s="61"/>
+      <c r="S7" s="61"/>
+      <c r="T7" s="61"/>
+      <c r="U7" s="61"/>
+      <c r="V7" s="61"/>
+      <c r="W7" s="61"/>
+      <c r="X7" s="61"/>
+      <c r="Y7" s="61"/>
+      <c r="Z7" s="61"/>
+      <c r="AA7" s="61"/>
+      <c r="AB7" s="61"/>
+      <c r="AC7" s="61"/>
+      <c r="AD7" s="61"/>
+      <c r="AE7" s="61"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:31">
+      <c r="A8" s="60"/>
+      <c r="B8" s="15"/>
       <c r="C8" s="61" t="s">
         <v>44</v>
       </c>
       <c r="D8" s="61"/>
-    </row>
-    <row r="9" customHeight="1" spans="1:4">
-      <c r="A9" s="13"/>
-      <c r="B9" s="69"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="61"/>
+      <c r="M8" s="61"/>
+      <c r="N8" s="61"/>
+      <c r="O8" s="61"/>
+      <c r="P8" s="61"/>
+      <c r="Q8" s="61"/>
+      <c r="R8" s="61"/>
+      <c r="S8" s="61"/>
+      <c r="T8" s="61"/>
+      <c r="U8" s="61"/>
+      <c r="V8" s="61"/>
+      <c r="W8" s="61"/>
+      <c r="X8" s="61"/>
+      <c r="Y8" s="61"/>
+      <c r="Z8" s="61"/>
+      <c r="AA8" s="61"/>
+      <c r="AB8" s="61"/>
+      <c r="AC8" s="61"/>
+      <c r="AD8" s="61"/>
+      <c r="AE8" s="61"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:31">
+      <c r="A9" s="60"/>
+      <c r="B9" s="15"/>
       <c r="C9" s="61"/>
       <c r="D9" s="61"/>
-    </row>
-    <row r="10" customHeight="1" spans="1:4">
-      <c r="A10" s="13"/>
-      <c r="B10" s="69" t="s">
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="61"/>
+      <c r="K9" s="61"/>
+      <c r="L9" s="61"/>
+      <c r="M9" s="61"/>
+      <c r="N9" s="61"/>
+      <c r="O9" s="61"/>
+      <c r="P9" s="61"/>
+      <c r="Q9" s="61"/>
+      <c r="R9" s="61"/>
+      <c r="S9" s="61"/>
+      <c r="T9" s="61"/>
+      <c r="U9" s="61"/>
+      <c r="V9" s="61"/>
+      <c r="W9" s="61"/>
+      <c r="X9" s="61"/>
+      <c r="Y9" s="61"/>
+      <c r="Z9" s="61"/>
+      <c r="AA9" s="61"/>
+      <c r="AB9" s="61"/>
+      <c r="AC9" s="61"/>
+      <c r="AD9" s="61"/>
+      <c r="AE9" s="61"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:31">
+      <c r="A10" s="60"/>
+      <c r="B10" s="15" t="s">
         <v>45</v>
       </c>
       <c r="C10" s="61"/>
       <c r="D10" s="61"/>
-    </row>
-    <row r="11" customHeight="1" spans="1:4">
-      <c r="A11" s="13"/>
-      <c r="B11" s="70"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="61"/>
+      <c r="K10" s="61"/>
+      <c r="L10" s="61"/>
+      <c r="M10" s="61"/>
+      <c r="N10" s="61"/>
+      <c r="O10" s="61"/>
+      <c r="P10" s="61"/>
+      <c r="Q10" s="61"/>
+      <c r="R10" s="61"/>
+      <c r="S10" s="61"/>
+      <c r="T10" s="61"/>
+      <c r="U10" s="61"/>
+      <c r="V10" s="61"/>
+      <c r="W10" s="61"/>
+      <c r="X10" s="61"/>
+      <c r="Y10" s="61"/>
+      <c r="Z10" s="61"/>
+      <c r="AA10" s="61"/>
+      <c r="AB10" s="61"/>
+      <c r="AC10" s="61"/>
+      <c r="AD10" s="61"/>
+      <c r="AE10" s="61"/>
+    </row>
+    <row r="11" customHeight="1" spans="1:31">
+      <c r="A11" s="60"/>
+      <c r="B11" s="69"/>
       <c r="C11" s="61" t="s">
         <v>46</v>
       </c>
       <c r="D11" s="61"/>
-    </row>
-    <row r="12" customHeight="1" spans="1:4">
-      <c r="A12" s="13"/>
-      <c r="B12" s="70"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="61"/>
+      <c r="K11" s="61"/>
+      <c r="L11" s="61"/>
+      <c r="M11" s="61"/>
+      <c r="N11" s="61"/>
+      <c r="O11" s="61"/>
+      <c r="P11" s="61"/>
+      <c r="Q11" s="61"/>
+      <c r="R11" s="61"/>
+      <c r="S11" s="61"/>
+      <c r="T11" s="61"/>
+      <c r="U11" s="61"/>
+      <c r="V11" s="61"/>
+      <c r="W11" s="61"/>
+      <c r="X11" s="61"/>
+      <c r="Y11" s="61"/>
+      <c r="Z11" s="61"/>
+      <c r="AA11" s="61"/>
+      <c r="AB11" s="61"/>
+      <c r="AC11" s="61"/>
+      <c r="AD11" s="61"/>
+      <c r="AE11" s="61"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:31">
+      <c r="A12" s="60"/>
+      <c r="B12" s="69"/>
       <c r="C12" s="61" t="s">
         <v>47</v>
       </c>
       <c r="D12" s="61"/>
-    </row>
-    <row r="13" customHeight="1" spans="1:4">
-      <c r="A13" s="13"/>
-      <c r="B13" s="70"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="61"/>
+      <c r="M12" s="61"/>
+      <c r="N12" s="61"/>
+      <c r="O12" s="61"/>
+      <c r="P12" s="61"/>
+      <c r="Q12" s="61"/>
+      <c r="R12" s="61"/>
+      <c r="S12" s="61"/>
+      <c r="T12" s="61"/>
+      <c r="U12" s="61"/>
+      <c r="V12" s="61"/>
+      <c r="W12" s="61"/>
+      <c r="X12" s="61"/>
+      <c r="Y12" s="61"/>
+      <c r="Z12" s="61"/>
+      <c r="AA12" s="61"/>
+      <c r="AB12" s="61"/>
+      <c r="AC12" s="61"/>
+      <c r="AD12" s="61"/>
+      <c r="AE12" s="61"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:31">
+      <c r="A13" s="60"/>
+      <c r="B13" s="69"/>
       <c r="C13" s="61" t="s">
         <v>48</v>
       </c>
       <c r="D13" s="61"/>
-    </row>
-    <row r="14" customHeight="1" spans="1:4">
-      <c r="A14" s="13"/>
-      <c r="B14" s="69"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="61"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="61"/>
+      <c r="K13" s="61"/>
+      <c r="L13" s="61"/>
+      <c r="M13" s="61"/>
+      <c r="N13" s="61"/>
+      <c r="O13" s="61"/>
+      <c r="P13" s="61"/>
+      <c r="Q13" s="61"/>
+      <c r="R13" s="61"/>
+      <c r="S13" s="61"/>
+      <c r="T13" s="61"/>
+      <c r="U13" s="61"/>
+      <c r="V13" s="61"/>
+      <c r="W13" s="61"/>
+      <c r="X13" s="61"/>
+      <c r="Y13" s="61"/>
+      <c r="Z13" s="61"/>
+      <c r="AA13" s="61"/>
+      <c r="AB13" s="61"/>
+      <c r="AC13" s="61"/>
+      <c r="AD13" s="61"/>
+      <c r="AE13" s="61"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:31">
+      <c r="A14" s="60"/>
+      <c r="B14" s="15"/>
       <c r="C14" s="61" t="s">
         <v>49</v>
       </c>
       <c r="D14" s="61"/>
-    </row>
-    <row r="15" customHeight="1" spans="1:4">
-      <c r="A15" s="13"/>
-      <c r="B15" s="69"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="61"/>
+      <c r="K14" s="61"/>
+      <c r="L14" s="61"/>
+      <c r="M14" s="61"/>
+      <c r="N14" s="61"/>
+      <c r="O14" s="61"/>
+      <c r="P14" s="61"/>
+      <c r="Q14" s="61"/>
+      <c r="R14" s="61"/>
+      <c r="S14" s="61"/>
+      <c r="T14" s="61"/>
+      <c r="U14" s="61"/>
+      <c r="V14" s="61"/>
+      <c r="W14" s="61"/>
+      <c r="X14" s="61"/>
+      <c r="Y14" s="61"/>
+      <c r="Z14" s="61"/>
+      <c r="AA14" s="61"/>
+      <c r="AB14" s="61"/>
+      <c r="AC14" s="61"/>
+      <c r="AD14" s="61"/>
+      <c r="AE14" s="61"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:31">
+      <c r="A15" s="60"/>
+      <c r="B15" s="15"/>
       <c r="C15" s="61" t="s">
         <v>50</v>
       </c>
       <c r="D15" s="61"/>
-    </row>
-    <row r="16" customHeight="1" spans="1:4">
-      <c r="A16" s="13"/>
-      <c r="B16" s="69"/>
+      <c r="E15" s="61"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="61"/>
+      <c r="I15" s="61"/>
+      <c r="J15" s="61"/>
+      <c r="K15" s="61"/>
+      <c r="L15" s="61"/>
+      <c r="M15" s="61"/>
+      <c r="N15" s="61"/>
+      <c r="O15" s="61"/>
+      <c r="P15" s="61"/>
+      <c r="Q15" s="61"/>
+      <c r="R15" s="61"/>
+      <c r="S15" s="61"/>
+      <c r="T15" s="61"/>
+      <c r="U15" s="61"/>
+      <c r="V15" s="61"/>
+      <c r="W15" s="61"/>
+      <c r="X15" s="61"/>
+      <c r="Y15" s="61"/>
+      <c r="Z15" s="61"/>
+      <c r="AA15" s="61"/>
+      <c r="AB15" s="61"/>
+      <c r="AC15" s="61"/>
+      <c r="AD15" s="61"/>
+      <c r="AE15" s="61"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:31">
+      <c r="A16" s="60"/>
+      <c r="B16" s="15"/>
       <c r="C16" s="61"/>
       <c r="D16" s="61"/>
-    </row>
-    <row r="17" customHeight="1" spans="1:4">
-      <c r="A17" s="13"/>
-      <c r="B17" s="69"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="61"/>
+      <c r="G16" s="61"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="61"/>
+      <c r="K16" s="61"/>
+      <c r="L16" s="61"/>
+      <c r="M16" s="61"/>
+      <c r="N16" s="61"/>
+      <c r="O16" s="61"/>
+      <c r="P16" s="61"/>
+      <c r="Q16" s="61"/>
+      <c r="R16" s="61"/>
+      <c r="S16" s="61"/>
+      <c r="T16" s="61"/>
+      <c r="U16" s="61"/>
+      <c r="V16" s="61"/>
+      <c r="W16" s="61"/>
+      <c r="X16" s="61"/>
+      <c r="Y16" s="61"/>
+      <c r="Z16" s="61"/>
+      <c r="AA16" s="61"/>
+      <c r="AB16" s="61"/>
+      <c r="AC16" s="61"/>
+      <c r="AD16" s="61"/>
+      <c r="AE16" s="61"/>
+    </row>
+    <row r="17" customHeight="1" spans="1:31">
+      <c r="A17" s="60"/>
+      <c r="B17" s="15"/>
       <c r="C17" s="61" t="s">
         <v>51</v>
       </c>
       <c r="D17" s="61"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:4">
-      <c r="A18" s="13"/>
-      <c r="B18" s="69"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="61"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="61"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="61"/>
+      <c r="K17" s="61"/>
+      <c r="L17" s="61"/>
+      <c r="M17" s="61"/>
+      <c r="N17" s="61"/>
+      <c r="O17" s="61"/>
+      <c r="P17" s="61"/>
+      <c r="Q17" s="61"/>
+      <c r="R17" s="61"/>
+      <c r="S17" s="61"/>
+      <c r="T17" s="61"/>
+      <c r="U17" s="61"/>
+      <c r="V17" s="61"/>
+      <c r="W17" s="61"/>
+      <c r="X17" s="61"/>
+      <c r="Y17" s="61"/>
+      <c r="Z17" s="61"/>
+      <c r="AA17" s="61"/>
+      <c r="AB17" s="61"/>
+      <c r="AC17" s="61"/>
+      <c r="AD17" s="61"/>
+      <c r="AE17" s="61"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:31">
+      <c r="A18" s="60"/>
+      <c r="B18" s="15"/>
       <c r="C18" s="61"/>
       <c r="D18" s="61"/>
-    </row>
-    <row r="19" customHeight="1" spans="1:4">
-      <c r="A19" s="13"/>
-      <c r="B19" s="69"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="61"/>
+      <c r="K18" s="61"/>
+      <c r="L18" s="61"/>
+      <c r="M18" s="61"/>
+      <c r="N18" s="61"/>
+      <c r="O18" s="61"/>
+      <c r="P18" s="61"/>
+      <c r="Q18" s="61"/>
+      <c r="R18" s="61"/>
+      <c r="S18" s="61"/>
+      <c r="T18" s="61"/>
+      <c r="U18" s="61"/>
+      <c r="V18" s="61"/>
+      <c r="W18" s="61"/>
+      <c r="X18" s="61"/>
+      <c r="Y18" s="61"/>
+      <c r="Z18" s="61"/>
+      <c r="AA18" s="61"/>
+      <c r="AB18" s="61"/>
+      <c r="AC18" s="61"/>
+      <c r="AD18" s="61"/>
+      <c r="AE18" s="61"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:31">
+      <c r="A19" s="60"/>
+      <c r="B19" s="15"/>
       <c r="C19" s="61" t="s">
         <v>52</v>
       </c>
       <c r="D19" s="61"/>
-    </row>
-    <row r="20" customHeight="1" spans="1:4">
-      <c r="A20" s="13"/>
-      <c r="B20" s="69"/>
+      <c r="E19" s="61"/>
+      <c r="F19" s="61"/>
+      <c r="G19" s="61"/>
+      <c r="H19" s="61"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="61"/>
+      <c r="K19" s="61"/>
+      <c r="L19" s="61"/>
+      <c r="M19" s="61"/>
+      <c r="N19" s="61"/>
+      <c r="O19" s="61"/>
+      <c r="P19" s="61"/>
+      <c r="Q19" s="61"/>
+      <c r="R19" s="61"/>
+      <c r="S19" s="61"/>
+      <c r="T19" s="61"/>
+      <c r="U19" s="61"/>
+      <c r="V19" s="61"/>
+      <c r="W19" s="61"/>
+      <c r="X19" s="61"/>
+      <c r="Y19" s="61"/>
+      <c r="Z19" s="61"/>
+      <c r="AA19" s="61"/>
+      <c r="AB19" s="61"/>
+      <c r="AC19" s="61"/>
+      <c r="AD19" s="61"/>
+      <c r="AE19" s="61"/>
+    </row>
+    <row r="20" customHeight="1" spans="1:31">
+      <c r="A20" s="60"/>
+      <c r="B20" s="15"/>
       <c r="C20" s="61" t="s">
         <v>53</v>
       </c>
       <c r="D20" s="61"/>
-    </row>
-    <row r="21" customHeight="1" spans="1:4">
-      <c r="A21" s="13"/>
-      <c r="B21" s="69"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="61"/>
+      <c r="K20" s="61"/>
+      <c r="L20" s="61"/>
+      <c r="M20" s="61"/>
+      <c r="N20" s="61"/>
+      <c r="O20" s="61"/>
+      <c r="P20" s="61"/>
+      <c r="Q20" s="61"/>
+      <c r="R20" s="61"/>
+      <c r="S20" s="61"/>
+      <c r="T20" s="61"/>
+      <c r="U20" s="61"/>
+      <c r="V20" s="61"/>
+      <c r="W20" s="61"/>
+      <c r="X20" s="61"/>
+      <c r="Y20" s="61"/>
+      <c r="Z20" s="61"/>
+      <c r="AA20" s="61"/>
+      <c r="AB20" s="61"/>
+      <c r="AC20" s="61"/>
+      <c r="AD20" s="61"/>
+      <c r="AE20" s="61"/>
+    </row>
+    <row r="21" customHeight="1" spans="1:31">
+      <c r="A21" s="60"/>
+      <c r="B21" s="15"/>
       <c r="C21" s="61" t="s">
         <v>54</v>
       </c>
       <c r="D21" s="61"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:4">
-      <c r="A22" s="13"/>
-      <c r="B22" s="69"/>
+      <c r="E21" s="61"/>
+      <c r="F21" s="61"/>
+      <c r="G21" s="61"/>
+      <c r="H21" s="61"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="61"/>
+      <c r="K21" s="61"/>
+      <c r="L21" s="61"/>
+      <c r="M21" s="61"/>
+      <c r="N21" s="61"/>
+      <c r="O21" s="61"/>
+      <c r="P21" s="61"/>
+      <c r="Q21" s="61"/>
+      <c r="R21" s="61"/>
+      <c r="S21" s="61"/>
+      <c r="T21" s="61"/>
+      <c r="U21" s="61"/>
+      <c r="V21" s="61"/>
+      <c r="W21" s="61"/>
+      <c r="X21" s="61"/>
+      <c r="Y21" s="61"/>
+      <c r="Z21" s="61"/>
+      <c r="AA21" s="61"/>
+      <c r="AB21" s="61"/>
+      <c r="AC21" s="61"/>
+      <c r="AD21" s="61"/>
+      <c r="AE21" s="61"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:31">
+      <c r="A22" s="60"/>
+      <c r="B22" s="15"/>
       <c r="C22" s="61" t="s">
         <v>55</v>
       </c>
       <c r="D22" s="61"/>
-    </row>
-    <row r="23" customHeight="1" spans="1:4">
-      <c r="A23" s="13"/>
-      <c r="B23" s="69"/>
+      <c r="E22" s="61"/>
+      <c r="F22" s="61"/>
+      <c r="G22" s="61"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="61"/>
+      <c r="K22" s="61"/>
+      <c r="L22" s="61"/>
+      <c r="M22" s="61"/>
+      <c r="N22" s="61"/>
+      <c r="O22" s="61"/>
+      <c r="P22" s="61"/>
+      <c r="Q22" s="61"/>
+      <c r="R22" s="61"/>
+      <c r="S22" s="61"/>
+      <c r="T22" s="61"/>
+      <c r="U22" s="61"/>
+      <c r="V22" s="61"/>
+      <c r="W22" s="61"/>
+      <c r="X22" s="61"/>
+      <c r="Y22" s="61"/>
+      <c r="Z22" s="61"/>
+      <c r="AA22" s="61"/>
+      <c r="AB22" s="61"/>
+      <c r="AC22" s="61"/>
+      <c r="AD22" s="61"/>
+      <c r="AE22" s="61"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:31">
+      <c r="A23" s="60"/>
+      <c r="B23" s="15"/>
       <c r="C23" s="61" t="s">
         <v>56</v>
       </c>
       <c r="D23" s="61"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:4">
-      <c r="A24" s="13"/>
-      <c r="B24" s="69"/>
+      <c r="E23" s="61"/>
+      <c r="F23" s="61"/>
+      <c r="G23" s="61"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="61"/>
+      <c r="K23" s="61"/>
+      <c r="L23" s="61"/>
+      <c r="M23" s="61"/>
+      <c r="N23" s="61"/>
+      <c r="O23" s="61"/>
+      <c r="P23" s="61"/>
+      <c r="Q23" s="61"/>
+      <c r="R23" s="61"/>
+      <c r="S23" s="61"/>
+      <c r="T23" s="61"/>
+      <c r="U23" s="61"/>
+      <c r="V23" s="61"/>
+      <c r="W23" s="61"/>
+      <c r="X23" s="61"/>
+      <c r="Y23" s="61"/>
+      <c r="Z23" s="61"/>
+      <c r="AA23" s="61"/>
+      <c r="AB23" s="61"/>
+      <c r="AC23" s="61"/>
+      <c r="AD23" s="61"/>
+      <c r="AE23" s="61"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:31">
+      <c r="A24" s="60"/>
+      <c r="B24" s="15"/>
       <c r="C24" s="61"/>
       <c r="D24" s="61" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="25" customHeight="1" spans="1:4">
-      <c r="A25" s="13"/>
-      <c r="B25" s="69"/>
+      <c r="E24" s="61"/>
+      <c r="F24" s="61"/>
+      <c r="G24" s="61"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="61"/>
+      <c r="J24" s="61"/>
+      <c r="K24" s="61"/>
+      <c r="L24" s="61"/>
+      <c r="M24" s="61"/>
+      <c r="N24" s="61"/>
+      <c r="O24" s="61"/>
+      <c r="P24" s="61"/>
+      <c r="Q24" s="61"/>
+      <c r="R24" s="61"/>
+      <c r="S24" s="61"/>
+      <c r="T24" s="61"/>
+      <c r="U24" s="61"/>
+      <c r="V24" s="61"/>
+      <c r="W24" s="61"/>
+      <c r="X24" s="61"/>
+      <c r="Y24" s="61"/>
+      <c r="Z24" s="61"/>
+      <c r="AA24" s="61"/>
+      <c r="AB24" s="61"/>
+      <c r="AC24" s="61"/>
+      <c r="AD24" s="61"/>
+      <c r="AE24" s="61"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:31">
+      <c r="A25" s="60"/>
+      <c r="B25" s="15"/>
       <c r="C25" s="61"/>
       <c r="D25" s="61" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="26" customHeight="1" spans="1:4">
-      <c r="A26" s="13"/>
-      <c r="B26" s="69"/>
+      <c r="E25" s="61"/>
+      <c r="F25" s="61"/>
+      <c r="G25" s="61"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="61"/>
+      <c r="J25" s="61"/>
+      <c r="K25" s="61"/>
+      <c r="L25" s="61"/>
+      <c r="M25" s="61"/>
+      <c r="N25" s="61"/>
+      <c r="O25" s="61"/>
+      <c r="P25" s="61"/>
+      <c r="Q25" s="61"/>
+      <c r="R25" s="61"/>
+      <c r="S25" s="61"/>
+      <c r="T25" s="61"/>
+      <c r="U25" s="61"/>
+      <c r="V25" s="61"/>
+      <c r="W25" s="61"/>
+      <c r="X25" s="61"/>
+      <c r="Y25" s="61"/>
+      <c r="Z25" s="61"/>
+      <c r="AA25" s="61"/>
+      <c r="AB25" s="61"/>
+      <c r="AC25" s="61"/>
+      <c r="AD25" s="61"/>
+      <c r="AE25" s="61"/>
+    </row>
+    <row r="26" customHeight="1" spans="1:31">
+      <c r="A26" s="60"/>
+      <c r="B26" s="15"/>
       <c r="C26" s="61"/>
       <c r="D26" s="61"/>
-    </row>
-    <row r="27" customHeight="1" spans="1:4">
-      <c r="A27" s="13"/>
-      <c r="B27" s="69"/>
+      <c r="E26" s="61"/>
+      <c r="F26" s="61"/>
+      <c r="G26" s="61"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="61"/>
+      <c r="K26" s="61"/>
+      <c r="L26" s="61"/>
+      <c r="M26" s="61"/>
+      <c r="N26" s="61"/>
+      <c r="O26" s="61"/>
+      <c r="P26" s="61"/>
+      <c r="Q26" s="61"/>
+      <c r="R26" s="61"/>
+      <c r="S26" s="61"/>
+      <c r="T26" s="61"/>
+      <c r="U26" s="61"/>
+      <c r="V26" s="61"/>
+      <c r="W26" s="61"/>
+      <c r="X26" s="61"/>
+      <c r="Y26" s="61"/>
+      <c r="Z26" s="61"/>
+      <c r="AA26" s="61"/>
+      <c r="AB26" s="61"/>
+      <c r="AC26" s="61"/>
+      <c r="AD26" s="61"/>
+      <c r="AE26" s="61"/>
+    </row>
+    <row r="27" customHeight="1" spans="1:31">
+      <c r="A27" s="60"/>
+      <c r="B27" s="15"/>
       <c r="C27" s="61" t="s">
         <v>59</v>
       </c>
       <c r="D27" s="61"/>
-    </row>
-    <row r="28" customHeight="1" spans="1:4">
-      <c r="A28" s="13"/>
-      <c r="B28" s="69"/>
+      <c r="E27" s="61"/>
+      <c r="F27" s="61"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="61"/>
+      <c r="J27" s="61"/>
+      <c r="K27" s="61"/>
+      <c r="L27" s="61"/>
+      <c r="M27" s="61"/>
+      <c r="N27" s="61"/>
+      <c r="O27" s="61"/>
+      <c r="P27" s="61"/>
+      <c r="Q27" s="61"/>
+      <c r="R27" s="61"/>
+      <c r="S27" s="61"/>
+      <c r="T27" s="61"/>
+      <c r="U27" s="61"/>
+      <c r="V27" s="61"/>
+      <c r="W27" s="61"/>
+      <c r="X27" s="61"/>
+      <c r="Y27" s="61"/>
+      <c r="Z27" s="61"/>
+      <c r="AA27" s="61"/>
+      <c r="AB27" s="61"/>
+      <c r="AC27" s="61"/>
+      <c r="AD27" s="61"/>
+      <c r="AE27" s="61"/>
+    </row>
+    <row r="28" customHeight="1" spans="1:31">
+      <c r="A28" s="60"/>
+      <c r="B28" s="15"/>
       <c r="C28" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="D28" s="71"/>
-    </row>
-    <row r="29" customHeight="1" spans="1:4">
-      <c r="A29" s="13"/>
-      <c r="B29" s="69"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="61"/>
+      <c r="F28" s="61"/>
+      <c r="G28" s="61"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="61"/>
+      <c r="J28" s="61"/>
+      <c r="K28" s="61"/>
+      <c r="L28" s="61"/>
+      <c r="M28" s="61"/>
+      <c r="N28" s="61"/>
+      <c r="O28" s="61"/>
+      <c r="P28" s="61"/>
+      <c r="Q28" s="61"/>
+      <c r="R28" s="61"/>
+      <c r="S28" s="61"/>
+      <c r="T28" s="61"/>
+      <c r="U28" s="61"/>
+      <c r="V28" s="61"/>
+      <c r="W28" s="61"/>
+      <c r="X28" s="61"/>
+      <c r="Y28" s="61"/>
+      <c r="Z28" s="61"/>
+      <c r="AA28" s="61"/>
+      <c r="AB28" s="61"/>
+      <c r="AC28" s="61"/>
+      <c r="AD28" s="61"/>
+      <c r="AE28" s="61"/>
+    </row>
+    <row r="29" customHeight="1" spans="1:31">
+      <c r="A29" s="60"/>
+      <c r="B29" s="15"/>
       <c r="C29" s="61" t="s">
         <v>61</v>
       </c>
       <c r="D29" s="61"/>
-    </row>
-    <row r="30" customHeight="1" spans="1:4">
-      <c r="A30" s="13"/>
-      <c r="B30" s="69"/>
+      <c r="E29" s="61"/>
+      <c r="F29" s="61"/>
+      <c r="G29" s="61"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="61"/>
+      <c r="J29" s="61"/>
+      <c r="K29" s="61"/>
+      <c r="L29" s="61"/>
+      <c r="M29" s="61"/>
+      <c r="N29" s="61"/>
+      <c r="O29" s="61"/>
+      <c r="P29" s="61"/>
+      <c r="Q29" s="61"/>
+      <c r="R29" s="61"/>
+      <c r="S29" s="61"/>
+      <c r="T29" s="61"/>
+      <c r="U29" s="61"/>
+      <c r="V29" s="61"/>
+      <c r="W29" s="61"/>
+      <c r="X29" s="61"/>
+      <c r="Y29" s="61"/>
+      <c r="Z29" s="61"/>
+      <c r="AA29" s="61"/>
+      <c r="AB29" s="61"/>
+      <c r="AC29" s="61"/>
+      <c r="AD29" s="61"/>
+      <c r="AE29" s="61"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:31">
+      <c r="A30" s="60"/>
+      <c r="B30" s="15"/>
       <c r="C30" s="61"/>
       <c r="D30" s="61"/>
-    </row>
-    <row r="31" customHeight="1" spans="1:4">
-      <c r="A31" s="13"/>
-      <c r="B31" s="69"/>
+      <c r="E30" s="61"/>
+      <c r="F30" s="61"/>
+      <c r="G30" s="61"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="61"/>
+      <c r="J30" s="61"/>
+      <c r="K30" s="61"/>
+      <c r="L30" s="61"/>
+      <c r="M30" s="61"/>
+      <c r="N30" s="61"/>
+      <c r="O30" s="61"/>
+      <c r="P30" s="61"/>
+      <c r="Q30" s="61"/>
+      <c r="R30" s="61"/>
+      <c r="S30" s="61"/>
+      <c r="T30" s="61"/>
+      <c r="U30" s="61"/>
+      <c r="V30" s="61"/>
+      <c r="W30" s="61"/>
+      <c r="X30" s="61"/>
+      <c r="Y30" s="61"/>
+      <c r="Z30" s="61"/>
+      <c r="AA30" s="61"/>
+      <c r="AB30" s="61"/>
+      <c r="AC30" s="61"/>
+      <c r="AD30" s="61"/>
+      <c r="AE30" s="61"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:31">
+      <c r="A31" s="60"/>
+      <c r="B31" s="15"/>
       <c r="C31" s="61" t="s">
         <v>56</v>
       </c>
       <c r="D31" s="61"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:4">
-      <c r="A32" s="13"/>
-      <c r="B32" s="69"/>
+      <c r="E31" s="61"/>
+      <c r="F31" s="61"/>
+      <c r="G31" s="61"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="61"/>
+      <c r="J31" s="61"/>
+      <c r="K31" s="61"/>
+      <c r="L31" s="61"/>
+      <c r="M31" s="61"/>
+      <c r="N31" s="61"/>
+      <c r="O31" s="61"/>
+      <c r="P31" s="61"/>
+      <c r="Q31" s="61"/>
+      <c r="R31" s="61"/>
+      <c r="S31" s="61"/>
+      <c r="T31" s="61"/>
+      <c r="U31" s="61"/>
+      <c r="V31" s="61"/>
+      <c r="W31" s="61"/>
+      <c r="X31" s="61"/>
+      <c r="Y31" s="61"/>
+      <c r="Z31" s="61"/>
+      <c r="AA31" s="61"/>
+      <c r="AB31" s="61"/>
+      <c r="AC31" s="61"/>
+      <c r="AD31" s="61"/>
+      <c r="AE31" s="61"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:31">
+      <c r="A32" s="60"/>
+      <c r="B32" s="15"/>
       <c r="C32" s="61"/>
       <c r="D32" s="61" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="33" customHeight="1" spans="1:4">
-      <c r="A33" s="13"/>
-      <c r="B33" s="69"/>
+      <c r="E32" s="61"/>
+      <c r="F32" s="61"/>
+      <c r="G32" s="61"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="61"/>
+      <c r="J32" s="61"/>
+      <c r="K32" s="61"/>
+      <c r="L32" s="61"/>
+      <c r="M32" s="61"/>
+      <c r="N32" s="61"/>
+      <c r="O32" s="61"/>
+      <c r="P32" s="61"/>
+      <c r="Q32" s="61"/>
+      <c r="R32" s="61"/>
+      <c r="S32" s="61"/>
+      <c r="T32" s="61"/>
+      <c r="U32" s="61"/>
+      <c r="V32" s="61"/>
+      <c r="W32" s="61"/>
+      <c r="X32" s="61"/>
+      <c r="Y32" s="61"/>
+      <c r="Z32" s="61"/>
+      <c r="AA32" s="61"/>
+      <c r="AB32" s="61"/>
+      <c r="AC32" s="61"/>
+      <c r="AD32" s="61"/>
+      <c r="AE32" s="61"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:31">
+      <c r="A33" s="60"/>
+      <c r="B33" s="15"/>
       <c r="C33" s="61"/>
       <c r="D33" s="61"/>
-    </row>
-    <row r="34" customHeight="1" spans="1:4">
-      <c r="A34" s="13"/>
-      <c r="B34" s="69" t="s">
+      <c r="E33" s="61"/>
+      <c r="F33" s="61"/>
+      <c r="G33" s="61"/>
+      <c r="H33" s="61"/>
+      <c r="I33" s="61"/>
+      <c r="J33" s="61"/>
+      <c r="K33" s="61"/>
+      <c r="L33" s="61"/>
+      <c r="M33" s="61"/>
+      <c r="N33" s="61"/>
+      <c r="O33" s="61"/>
+      <c r="P33" s="61"/>
+      <c r="Q33" s="61"/>
+      <c r="R33" s="61"/>
+      <c r="S33" s="61"/>
+      <c r="T33" s="61"/>
+      <c r="U33" s="61"/>
+      <c r="V33" s="61"/>
+      <c r="W33" s="61"/>
+      <c r="X33" s="61"/>
+      <c r="Y33" s="61"/>
+      <c r="Z33" s="61"/>
+      <c r="AA33" s="61"/>
+      <c r="AB33" s="61"/>
+      <c r="AC33" s="61"/>
+      <c r="AD33" s="61"/>
+      <c r="AE33" s="61"/>
+    </row>
+    <row r="34" customHeight="1" spans="1:31">
+      <c r="A34" s="60"/>
+      <c r="B34" s="15" t="s">
         <v>63</v>
       </c>
       <c r="C34" s="61"/>
       <c r="D34" s="61"/>
-    </row>
-    <row r="35" customHeight="1" spans="1:19">
-      <c r="A35" s="13"/>
-      <c r="B35" s="69"/>
-      <c r="C35" s="72" t="s">
+      <c r="E34" s="61"/>
+      <c r="F34" s="61"/>
+      <c r="G34" s="61"/>
+      <c r="H34" s="61"/>
+      <c r="I34" s="61"/>
+      <c r="J34" s="61"/>
+      <c r="K34" s="61"/>
+      <c r="L34" s="61"/>
+      <c r="M34" s="61"/>
+      <c r="N34" s="61"/>
+      <c r="O34" s="61"/>
+      <c r="P34" s="61"/>
+      <c r="Q34" s="61"/>
+      <c r="R34" s="61"/>
+      <c r="S34" s="61"/>
+      <c r="T34" s="61"/>
+      <c r="U34" s="61"/>
+      <c r="V34" s="61"/>
+      <c r="W34" s="61"/>
+      <c r="X34" s="61"/>
+      <c r="Y34" s="61"/>
+      <c r="Z34" s="61"/>
+      <c r="AA34" s="61"/>
+      <c r="AB34" s="61"/>
+      <c r="AC34" s="61"/>
+      <c r="AD34" s="61"/>
+      <c r="AE34" s="61"/>
+    </row>
+    <row r="35" customHeight="1" spans="1:31">
+      <c r="A35" s="60"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="D35" s="72"/>
-      <c r="E35" s="72"/>
-      <c r="F35" s="72"/>
-      <c r="G35" s="72" t="s">
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71" t="s">
         <v>65</v>
       </c>
-      <c r="H35" s="72"/>
-      <c r="I35" s="72"/>
-      <c r="J35" s="72"/>
-      <c r="K35" s="72"/>
-      <c r="L35" s="86" t="s">
+      <c r="H35" s="71"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="71"/>
+      <c r="L35" s="71" t="s">
         <v>66</v>
       </c>
-      <c r="M35" s="86"/>
-      <c r="N35" s="86"/>
-      <c r="O35" s="86"/>
-      <c r="P35" s="86"/>
-      <c r="Q35" s="86"/>
-      <c r="R35" s="86"/>
-      <c r="S35" s="86"/>
-    </row>
-    <row r="36" customHeight="1" spans="1:19">
-      <c r="A36" s="13"/>
-      <c r="B36" s="69"/>
+      <c r="M35" s="71"/>
+      <c r="N35" s="71"/>
+      <c r="O35" s="71"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="71"/>
+      <c r="S35" s="71"/>
+      <c r="T35" s="61"/>
+      <c r="U35" s="61"/>
+      <c r="V35" s="61"/>
+      <c r="W35" s="61"/>
+      <c r="X35" s="61"/>
+      <c r="Y35" s="61"/>
+      <c r="Z35" s="61"/>
+      <c r="AA35" s="61"/>
+      <c r="AB35" s="61"/>
+      <c r="AC35" s="61"/>
+      <c r="AD35" s="61"/>
+      <c r="AE35" s="61"/>
+    </row>
+    <row r="36" customHeight="1" spans="1:31">
+      <c r="A36" s="60"/>
+      <c r="B36" s="15"/>
       <c r="C36" s="57" t="s">
         <v>67</v>
       </c>
@@ -4754,20 +5470,32 @@
       <c r="I36" s="57"/>
       <c r="J36" s="57"/>
       <c r="K36" s="57"/>
-      <c r="L36" s="49" t="s">
+      <c r="L36" s="57" t="s">
         <v>69</v>
       </c>
-      <c r="M36" s="49"/>
-      <c r="N36" s="49"/>
-      <c r="O36" s="49"/>
-      <c r="P36" s="49"/>
-      <c r="Q36" s="49"/>
-      <c r="R36" s="49"/>
-      <c r="S36" s="49"/>
-    </row>
-    <row r="37" customHeight="1" spans="1:19">
-      <c r="A37" s="13"/>
-      <c r="B37" s="69"/>
+      <c r="M36" s="57"/>
+      <c r="N36" s="57"/>
+      <c r="O36" s="57"/>
+      <c r="P36" s="57"/>
+      <c r="Q36" s="57"/>
+      <c r="R36" s="57"/>
+      <c r="S36" s="57"/>
+      <c r="T36" s="61"/>
+      <c r="U36" s="61"/>
+      <c r="V36" s="61"/>
+      <c r="W36" s="61"/>
+      <c r="X36" s="61"/>
+      <c r="Y36" s="61"/>
+      <c r="Z36" s="61"/>
+      <c r="AA36" s="61"/>
+      <c r="AB36" s="61"/>
+      <c r="AC36" s="61"/>
+      <c r="AD36" s="61"/>
+      <c r="AE36" s="61"/>
+    </row>
+    <row r="37" customHeight="1" spans="1:31">
+      <c r="A37" s="60"/>
+      <c r="B37" s="15"/>
       <c r="C37" s="57" t="s">
         <v>70</v>
       </c>
@@ -4781,458 +5509,814 @@
       <c r="I37" s="57"/>
       <c r="J37" s="57"/>
       <c r="K37" s="57"/>
-      <c r="L37" s="49" t="s">
+      <c r="L37" s="57" t="s">
         <v>72</v>
       </c>
-      <c r="M37" s="49"/>
-      <c r="N37" s="49"/>
-      <c r="O37" s="49"/>
-      <c r="P37" s="49"/>
-      <c r="Q37" s="49"/>
-      <c r="R37" s="49"/>
-      <c r="S37" s="49"/>
-    </row>
-    <row r="38" customHeight="1" spans="1:19">
-      <c r="A38" s="13"/>
-      <c r="B38" s="70"/>
-      <c r="C38" s="73" t="s">
+      <c r="M37" s="57"/>
+      <c r="N37" s="57"/>
+      <c r="O37" s="57"/>
+      <c r="P37" s="57"/>
+      <c r="Q37" s="57"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="61"/>
+      <c r="U37" s="61"/>
+      <c r="V37" s="61"/>
+      <c r="W37" s="61"/>
+      <c r="X37" s="61"/>
+      <c r="Y37" s="61"/>
+      <c r="Z37" s="61"/>
+      <c r="AA37" s="61"/>
+      <c r="AB37" s="61"/>
+      <c r="AC37" s="61"/>
+      <c r="AD37" s="61"/>
+      <c r="AE37" s="61"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:31">
+      <c r="A38" s="60"/>
+      <c r="B38" s="69"/>
+      <c r="C38" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="D38" s="73"/>
-      <c r="E38" s="73"/>
-      <c r="F38" s="73"/>
-      <c r="G38" s="74" t="s">
+      <c r="D38" s="72"/>
+      <c r="E38" s="72"/>
+      <c r="F38" s="72"/>
+      <c r="G38" s="73" t="s">
         <v>74</v>
       </c>
-      <c r="H38" s="74"/>
-      <c r="I38" s="74"/>
-      <c r="J38" s="74"/>
-      <c r="K38" s="74"/>
-      <c r="L38" s="49" t="s">
+      <c r="H38" s="73"/>
+      <c r="I38" s="73"/>
+      <c r="J38" s="73"/>
+      <c r="K38" s="73"/>
+      <c r="L38" s="57" t="s">
         <v>75</v>
       </c>
-      <c r="M38" s="49"/>
-      <c r="N38" s="49"/>
-      <c r="O38" s="49"/>
-      <c r="P38" s="49"/>
-      <c r="Q38" s="49"/>
-      <c r="R38" s="49"/>
-      <c r="S38" s="49"/>
-    </row>
-    <row r="39" customHeight="1" spans="1:19">
-      <c r="A39" s="13"/>
-      <c r="B39" s="70"/>
-      <c r="C39" s="74" t="s">
+      <c r="M38" s="57"/>
+      <c r="N38" s="57"/>
+      <c r="O38" s="57"/>
+      <c r="P38" s="57"/>
+      <c r="Q38" s="57"/>
+      <c r="R38" s="57"/>
+      <c r="S38" s="57"/>
+      <c r="T38" s="61"/>
+      <c r="U38" s="61"/>
+      <c r="V38" s="61"/>
+      <c r="W38" s="61"/>
+      <c r="X38" s="61"/>
+      <c r="Y38" s="61"/>
+      <c r="Z38" s="61"/>
+      <c r="AA38" s="61"/>
+      <c r="AB38" s="61"/>
+      <c r="AC38" s="61"/>
+      <c r="AD38" s="61"/>
+      <c r="AE38" s="61"/>
+    </row>
+    <row r="39" customHeight="1" spans="1:31">
+      <c r="A39" s="60"/>
+      <c r="B39" s="69"/>
+      <c r="C39" s="73" t="s">
         <v>76</v>
       </c>
-      <c r="D39" s="74"/>
-      <c r="E39" s="74"/>
-      <c r="F39" s="74"/>
-      <c r="G39" s="74" t="s">
+      <c r="D39" s="73"/>
+      <c r="E39" s="73"/>
+      <c r="F39" s="73"/>
+      <c r="G39" s="73" t="s">
         <v>77</v>
       </c>
-      <c r="H39" s="74"/>
-      <c r="I39" s="74"/>
-      <c r="J39" s="74"/>
-      <c r="K39" s="74"/>
-      <c r="L39" s="49" t="s">
+      <c r="H39" s="73"/>
+      <c r="I39" s="73"/>
+      <c r="J39" s="73"/>
+      <c r="K39" s="73"/>
+      <c r="L39" s="57" t="s">
         <v>78</v>
       </c>
-      <c r="M39" s="49"/>
-      <c r="N39" s="49"/>
-      <c r="O39" s="49"/>
-      <c r="P39" s="49"/>
-      <c r="Q39" s="49"/>
-      <c r="R39" s="49"/>
-      <c r="S39" s="49"/>
-    </row>
-    <row r="40" customHeight="1" spans="1:19">
-      <c r="A40" s="13"/>
-      <c r="B40" s="70"/>
-      <c r="C40" s="75" t="s">
+      <c r="M39" s="57"/>
+      <c r="N39" s="57"/>
+      <c r="O39" s="57"/>
+      <c r="P39" s="57"/>
+      <c r="Q39" s="57"/>
+      <c r="R39" s="57"/>
+      <c r="S39" s="57"/>
+      <c r="T39" s="61"/>
+      <c r="U39" s="61"/>
+      <c r="V39" s="61"/>
+      <c r="W39" s="61"/>
+      <c r="X39" s="61"/>
+      <c r="Y39" s="61"/>
+      <c r="Z39" s="61"/>
+      <c r="AA39" s="61"/>
+      <c r="AB39" s="61"/>
+      <c r="AC39" s="61"/>
+      <c r="AD39" s="61"/>
+      <c r="AE39" s="61"/>
+    </row>
+    <row r="40" customHeight="1" spans="1:31">
+      <c r="A40" s="60"/>
+      <c r="B40" s="69"/>
+      <c r="C40" s="74" t="s">
         <v>79</v>
       </c>
-      <c r="D40" s="75"/>
-      <c r="E40" s="75"/>
-      <c r="F40" s="75"/>
-      <c r="G40" s="75" t="s">
+      <c r="D40" s="74"/>
+      <c r="E40" s="74"/>
+      <c r="F40" s="74"/>
+      <c r="G40" s="74" t="s">
         <v>80</v>
       </c>
-      <c r="H40" s="75"/>
-      <c r="I40" s="75"/>
-      <c r="J40" s="75"/>
-      <c r="K40" s="75"/>
-      <c r="L40" s="87" t="s">
+      <c r="H40" s="74"/>
+      <c r="I40" s="74"/>
+      <c r="J40" s="74"/>
+      <c r="K40" s="74"/>
+      <c r="L40" s="80" t="s">
         <v>81</v>
       </c>
-      <c r="M40" s="87"/>
-      <c r="N40" s="87"/>
-      <c r="O40" s="87"/>
-      <c r="P40" s="87"/>
-      <c r="Q40" s="87"/>
-      <c r="R40" s="87"/>
-      <c r="S40" s="87"/>
-    </row>
-    <row r="41" customHeight="1" spans="1:19">
-      <c r="A41" s="13"/>
-      <c r="B41" s="70"/>
-      <c r="C41" s="76"/>
-      <c r="D41" s="76"/>
-      <c r="E41" s="76"/>
-      <c r="F41" s="76"/>
-      <c r="G41" s="76"/>
-      <c r="H41" s="76"/>
-      <c r="I41" s="76"/>
-      <c r="J41" s="76"/>
-      <c r="K41" s="76"/>
-      <c r="L41" s="88"/>
-      <c r="M41" s="88"/>
-      <c r="N41" s="88"/>
-      <c r="O41" s="88"/>
-      <c r="P41" s="88"/>
-      <c r="Q41" s="88"/>
-      <c r="R41" s="88"/>
-      <c r="S41" s="88"/>
-    </row>
-    <row r="42" customHeight="1" spans="1:19">
-      <c r="A42" s="13"/>
-      <c r="B42" s="77" t="s">
+      <c r="M40" s="80"/>
+      <c r="N40" s="80"/>
+      <c r="O40" s="80"/>
+      <c r="P40" s="80"/>
+      <c r="Q40" s="80"/>
+      <c r="R40" s="80"/>
+      <c r="S40" s="80"/>
+      <c r="T40" s="61"/>
+      <c r="U40" s="61"/>
+      <c r="V40" s="61"/>
+      <c r="W40" s="61"/>
+      <c r="X40" s="61"/>
+      <c r="Y40" s="61"/>
+      <c r="Z40" s="61"/>
+      <c r="AA40" s="61"/>
+      <c r="AB40" s="61"/>
+      <c r="AC40" s="61"/>
+      <c r="AD40" s="61"/>
+      <c r="AE40" s="61"/>
+    </row>
+    <row r="41" customHeight="1" spans="1:31">
+      <c r="A41" s="60"/>
+      <c r="B41" s="69"/>
+      <c r="C41" s="75"/>
+      <c r="D41" s="75"/>
+      <c r="E41" s="75"/>
+      <c r="F41" s="75"/>
+      <c r="G41" s="75"/>
+      <c r="H41" s="75"/>
+      <c r="I41" s="75"/>
+      <c r="J41" s="75"/>
+      <c r="K41" s="75"/>
+      <c r="L41" s="83"/>
+      <c r="M41" s="83"/>
+      <c r="N41" s="83"/>
+      <c r="O41" s="83"/>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83"/>
+      <c r="R41" s="83"/>
+      <c r="S41" s="83"/>
+      <c r="T41" s="61"/>
+      <c r="U41" s="61"/>
+      <c r="V41" s="61"/>
+      <c r="W41" s="61"/>
+      <c r="X41" s="61"/>
+      <c r="Y41" s="61"/>
+      <c r="Z41" s="61"/>
+      <c r="AA41" s="61"/>
+      <c r="AB41" s="61"/>
+      <c r="AC41" s="61"/>
+      <c r="AD41" s="61"/>
+      <c r="AE41" s="61"/>
+    </row>
+    <row r="42" customHeight="1" spans="1:31">
+      <c r="A42" s="60"/>
+      <c r="B42" s="76" t="s">
         <v>82</v>
       </c>
-      <c r="C42" s="78"/>
-      <c r="D42" s="78"/>
-      <c r="E42" s="78"/>
-      <c r="F42" s="78"/>
-      <c r="G42" s="78"/>
-      <c r="H42" s="78"/>
-      <c r="I42" s="78"/>
-      <c r="J42" s="78"/>
-      <c r="K42" s="78"/>
-      <c r="L42" s="89"/>
-      <c r="M42" s="89"/>
-      <c r="N42" s="89"/>
-      <c r="O42" s="89"/>
-      <c r="P42" s="89"/>
-      <c r="Q42" s="89"/>
-      <c r="R42" s="89"/>
-      <c r="S42" s="89"/>
-    </row>
-    <row r="43" customHeight="1" spans="1:19">
-      <c r="A43" s="13"/>
-      <c r="B43" s="79"/>
-      <c r="C43" s="80" t="s">
+      <c r="C42" s="77"/>
+      <c r="D42" s="77"/>
+      <c r="E42" s="77"/>
+      <c r="F42" s="77"/>
+      <c r="G42" s="77"/>
+      <c r="H42" s="77"/>
+      <c r="I42" s="77"/>
+      <c r="J42" s="77"/>
+      <c r="K42" s="77"/>
+      <c r="L42" s="84"/>
+      <c r="M42" s="84"/>
+      <c r="N42" s="84"/>
+      <c r="O42" s="84"/>
+      <c r="P42" s="84"/>
+      <c r="Q42" s="84"/>
+      <c r="R42" s="84"/>
+      <c r="S42" s="84"/>
+      <c r="T42" s="61"/>
+      <c r="U42" s="61"/>
+      <c r="V42" s="61"/>
+      <c r="W42" s="61"/>
+      <c r="X42" s="61"/>
+      <c r="Y42" s="61"/>
+      <c r="Z42" s="61"/>
+      <c r="AA42" s="61"/>
+      <c r="AB42" s="61"/>
+      <c r="AC42" s="61"/>
+      <c r="AD42" s="61"/>
+      <c r="AE42" s="61"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:31">
+      <c r="A43" s="60"/>
+      <c r="B43" s="78"/>
+      <c r="C43" s="79" t="s">
         <v>83</v>
       </c>
-      <c r="D43" s="80"/>
-      <c r="E43" s="80"/>
-      <c r="F43" s="80"/>
-      <c r="G43" s="80" t="s">
+      <c r="D43" s="79"/>
+      <c r="E43" s="79"/>
+      <c r="F43" s="79"/>
+      <c r="G43" s="79" t="s">
         <v>84</v>
       </c>
-      <c r="H43" s="80"/>
-      <c r="I43" s="80"/>
-      <c r="J43" s="80"/>
-      <c r="K43" s="80"/>
-      <c r="L43" s="90" t="s">
+      <c r="H43" s="79"/>
+      <c r="I43" s="79"/>
+      <c r="J43" s="79"/>
+      <c r="K43" s="79"/>
+      <c r="L43" s="85" t="s">
         <v>85</v>
       </c>
-      <c r="M43" s="91"/>
-      <c r="N43" s="92"/>
-      <c r="O43" s="90" t="s">
+      <c r="M43" s="86"/>
+      <c r="N43" s="87"/>
+      <c r="O43" s="85" t="s">
         <v>66</v>
       </c>
-      <c r="P43" s="91"/>
-      <c r="Q43" s="91"/>
-      <c r="R43" s="91"/>
-      <c r="S43" s="92"/>
-    </row>
-    <row r="44" customHeight="1" spans="1:19">
-      <c r="A44" s="13"/>
-      <c r="B44" s="79"/>
-      <c r="C44" s="81" t="s">
+      <c r="P43" s="86"/>
+      <c r="Q43" s="86"/>
+      <c r="R43" s="86"/>
+      <c r="S43" s="87"/>
+      <c r="T43" s="61"/>
+      <c r="U43" s="61"/>
+      <c r="V43" s="61"/>
+      <c r="W43" s="61"/>
+      <c r="X43" s="61"/>
+      <c r="Y43" s="61"/>
+      <c r="Z43" s="61"/>
+      <c r="AA43" s="61"/>
+      <c r="AB43" s="61"/>
+      <c r="AC43" s="61"/>
+      <c r="AD43" s="61"/>
+      <c r="AE43" s="61"/>
+    </row>
+    <row r="44" customHeight="1" spans="1:31">
+      <c r="A44" s="60"/>
+      <c r="B44" s="78"/>
+      <c r="C44" s="80" t="s">
         <v>86</v>
       </c>
-      <c r="D44" s="81"/>
-      <c r="E44" s="81"/>
-      <c r="F44" s="81"/>
-      <c r="G44" s="81" t="s">
+      <c r="D44" s="80"/>
+      <c r="E44" s="80"/>
+      <c r="F44" s="80"/>
+      <c r="G44" s="80" t="s">
         <v>87</v>
       </c>
-      <c r="H44" s="81"/>
-      <c r="I44" s="81"/>
-      <c r="J44" s="81"/>
-      <c r="K44" s="81"/>
-      <c r="L44" s="93" t="s">
+      <c r="H44" s="80"/>
+      <c r="I44" s="80"/>
+      <c r="J44" s="80"/>
+      <c r="K44" s="80"/>
+      <c r="L44" s="88" t="s">
         <v>88</v>
       </c>
-      <c r="M44" s="94"/>
-      <c r="N44" s="95"/>
-      <c r="O44" s="93" t="s">
+      <c r="M44" s="89"/>
+      <c r="N44" s="90"/>
+      <c r="O44" s="88" t="s">
         <v>89</v>
       </c>
-      <c r="P44" s="94"/>
-      <c r="Q44" s="94"/>
-      <c r="R44" s="94"/>
-      <c r="S44" s="95"/>
-    </row>
-    <row r="45" customHeight="1" spans="1:19">
-      <c r="A45" s="13"/>
-      <c r="B45" s="79"/>
-      <c r="C45" s="81" t="s">
+      <c r="P44" s="89"/>
+      <c r="Q44" s="89"/>
+      <c r="R44" s="89"/>
+      <c r="S44" s="90"/>
+      <c r="T44" s="61"/>
+      <c r="U44" s="61"/>
+      <c r="V44" s="61"/>
+      <c r="W44" s="61"/>
+      <c r="X44" s="61"/>
+      <c r="Y44" s="61"/>
+      <c r="Z44" s="61"/>
+      <c r="AA44" s="61"/>
+      <c r="AB44" s="61"/>
+      <c r="AC44" s="61"/>
+      <c r="AD44" s="61"/>
+      <c r="AE44" s="61"/>
+    </row>
+    <row r="45" customHeight="1" spans="1:31">
+      <c r="A45" s="60"/>
+      <c r="B45" s="78"/>
+      <c r="C45" s="80" t="s">
         <v>90</v>
       </c>
-      <c r="D45" s="81"/>
-      <c r="E45" s="81"/>
-      <c r="F45" s="81"/>
-      <c r="G45" s="81" t="s">
+      <c r="D45" s="80"/>
+      <c r="E45" s="80"/>
+      <c r="F45" s="80"/>
+      <c r="G45" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="H45" s="81"/>
-      <c r="I45" s="81"/>
-      <c r="J45" s="81"/>
-      <c r="K45" s="81"/>
-      <c r="L45" s="93" t="s">
+      <c r="H45" s="80"/>
+      <c r="I45" s="80"/>
+      <c r="J45" s="80"/>
+      <c r="K45" s="80"/>
+      <c r="L45" s="88" t="s">
         <v>88</v>
       </c>
-      <c r="M45" s="94"/>
-      <c r="N45" s="95"/>
-      <c r="O45" s="93" t="s">
+      <c r="M45" s="89"/>
+      <c r="N45" s="90"/>
+      <c r="O45" s="88" t="s">
         <v>89</v>
       </c>
-      <c r="P45" s="94"/>
-      <c r="Q45" s="94"/>
-      <c r="R45" s="94"/>
-      <c r="S45" s="95"/>
-    </row>
-    <row r="46" customHeight="1" spans="1:19">
-      <c r="A46" s="13"/>
-      <c r="B46" s="79"/>
-      <c r="C46" s="82" t="s">
+      <c r="P45" s="89"/>
+      <c r="Q45" s="89"/>
+      <c r="R45" s="89"/>
+      <c r="S45" s="90"/>
+      <c r="T45" s="61"/>
+      <c r="U45" s="61"/>
+      <c r="V45" s="61"/>
+      <c r="W45" s="61"/>
+      <c r="X45" s="61"/>
+      <c r="Y45" s="61"/>
+      <c r="Z45" s="61"/>
+      <c r="AA45" s="61"/>
+      <c r="AB45" s="61"/>
+      <c r="AC45" s="61"/>
+      <c r="AD45" s="61"/>
+      <c r="AE45" s="61"/>
+    </row>
+    <row r="46" customHeight="1" spans="1:31">
+      <c r="A46" s="60"/>
+      <c r="B46" s="78"/>
+      <c r="C46" s="74" t="s">
         <v>92</v>
       </c>
-      <c r="D46" s="82"/>
-      <c r="E46" s="82"/>
-      <c r="F46" s="82"/>
-      <c r="G46" s="75" t="s">
+      <c r="D46" s="74"/>
+      <c r="E46" s="74"/>
+      <c r="F46" s="74"/>
+      <c r="G46" s="74" t="s">
         <v>93</v>
       </c>
-      <c r="H46" s="75"/>
-      <c r="I46" s="75"/>
-      <c r="J46" s="75"/>
-      <c r="K46" s="75"/>
-      <c r="L46" s="93" t="s">
+      <c r="H46" s="74"/>
+      <c r="I46" s="74"/>
+      <c r="J46" s="74"/>
+      <c r="K46" s="74"/>
+      <c r="L46" s="88" t="s">
         <v>88</v>
       </c>
-      <c r="M46" s="94"/>
-      <c r="N46" s="95"/>
-      <c r="O46" s="96" t="s">
+      <c r="M46" s="89"/>
+      <c r="N46" s="90"/>
+      <c r="O46" s="88" t="s">
         <v>94</v>
       </c>
-      <c r="P46" s="97"/>
-      <c r="Q46" s="97"/>
-      <c r="R46" s="97"/>
-      <c r="S46" s="100"/>
-    </row>
-    <row r="47" customHeight="1" spans="1:19">
-      <c r="A47" s="13"/>
-      <c r="B47" s="79"/>
-      <c r="C47" s="75" t="s">
+      <c r="P46" s="89"/>
+      <c r="Q46" s="89"/>
+      <c r="R46" s="89"/>
+      <c r="S46" s="90"/>
+      <c r="T46" s="61"/>
+      <c r="U46" s="61"/>
+      <c r="V46" s="61"/>
+      <c r="W46" s="61"/>
+      <c r="X46" s="61"/>
+      <c r="Y46" s="61"/>
+      <c r="Z46" s="61"/>
+      <c r="AA46" s="61"/>
+      <c r="AB46" s="61"/>
+      <c r="AC46" s="61"/>
+      <c r="AD46" s="61"/>
+      <c r="AE46" s="61"/>
+    </row>
+    <row r="47" customHeight="1" spans="1:31">
+      <c r="A47" s="60"/>
+      <c r="B47" s="78"/>
+      <c r="C47" s="74" t="s">
         <v>95</v>
       </c>
-      <c r="D47" s="75"/>
-      <c r="E47" s="75"/>
-      <c r="F47" s="75"/>
-      <c r="G47" s="75" t="s">
+      <c r="D47" s="74"/>
+      <c r="E47" s="74"/>
+      <c r="F47" s="74"/>
+      <c r="G47" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="H47" s="75"/>
-      <c r="I47" s="75"/>
-      <c r="J47" s="75"/>
-      <c r="K47" s="75"/>
-      <c r="L47" s="93" t="s">
+      <c r="H47" s="74"/>
+      <c r="I47" s="74"/>
+      <c r="J47" s="74"/>
+      <c r="K47" s="74"/>
+      <c r="L47" s="88" t="s">
         <v>88</v>
       </c>
-      <c r="M47" s="94"/>
-      <c r="N47" s="95"/>
-      <c r="O47" s="96" t="s">
+      <c r="M47" s="89"/>
+      <c r="N47" s="90"/>
+      <c r="O47" s="88" t="s">
         <v>94</v>
       </c>
-      <c r="P47" s="97"/>
-      <c r="Q47" s="97"/>
-      <c r="R47" s="97"/>
-      <c r="S47" s="100"/>
-    </row>
-    <row r="48" customHeight="1" spans="1:19">
-      <c r="A48" s="13"/>
-      <c r="B48" s="77"/>
-      <c r="C48" s="75" t="s">
+      <c r="P47" s="89"/>
+      <c r="Q47" s="89"/>
+      <c r="R47" s="89"/>
+      <c r="S47" s="90"/>
+      <c r="T47" s="61"/>
+      <c r="U47" s="61"/>
+      <c r="V47" s="61"/>
+      <c r="W47" s="61"/>
+      <c r="X47" s="61"/>
+      <c r="Y47" s="61"/>
+      <c r="Z47" s="61"/>
+      <c r="AA47" s="61"/>
+      <c r="AB47" s="61"/>
+      <c r="AC47" s="61"/>
+      <c r="AD47" s="61"/>
+      <c r="AE47" s="61"/>
+    </row>
+    <row r="48" customHeight="1" spans="1:31">
+      <c r="A48" s="60"/>
+      <c r="B48" s="76"/>
+      <c r="C48" s="74" t="s">
         <v>97</v>
       </c>
-      <c r="D48" s="75"/>
-      <c r="E48" s="75"/>
-      <c r="F48" s="75"/>
-      <c r="G48" s="75" t="s">
+      <c r="D48" s="74"/>
+      <c r="E48" s="74"/>
+      <c r="F48" s="74"/>
+      <c r="G48" s="74" t="s">
         <v>98</v>
       </c>
-      <c r="H48" s="75"/>
-      <c r="I48" s="75"/>
-      <c r="J48" s="75"/>
-      <c r="K48" s="75"/>
-      <c r="L48" s="93" t="s">
+      <c r="H48" s="74"/>
+      <c r="I48" s="74"/>
+      <c r="J48" s="74"/>
+      <c r="K48" s="74"/>
+      <c r="L48" s="88" t="s">
         <v>88</v>
       </c>
-      <c r="M48" s="94"/>
-      <c r="N48" s="95"/>
-      <c r="O48" s="96" t="s">
+      <c r="M48" s="89"/>
+      <c r="N48" s="90"/>
+      <c r="O48" s="88" t="s">
         <v>99</v>
       </c>
-      <c r="P48" s="97"/>
-      <c r="Q48" s="97"/>
-      <c r="R48" s="97"/>
-      <c r="S48" s="100"/>
-    </row>
-    <row r="49" customHeight="1" spans="1:19">
-      <c r="A49" s="13"/>
-      <c r="B49" s="69"/>
-      <c r="C49" s="78"/>
-      <c r="D49" s="78"/>
-      <c r="E49" s="78"/>
-      <c r="F49" s="78"/>
-      <c r="G49" s="78"/>
-      <c r="H49" s="78"/>
-      <c r="I49" s="78"/>
-      <c r="J49" s="78"/>
-      <c r="K49" s="78"/>
-      <c r="L49" s="89"/>
-      <c r="M49" s="89"/>
-      <c r="N49" s="89"/>
-      <c r="O49" s="89"/>
-      <c r="P49" s="89"/>
-      <c r="Q49" s="89"/>
-      <c r="R49" s="89"/>
-      <c r="S49" s="89"/>
-    </row>
-    <row r="50" customHeight="1" spans="1:17">
-      <c r="A50" s="13"/>
-      <c r="B50" s="77" t="s">
+      <c r="P48" s="89"/>
+      <c r="Q48" s="89"/>
+      <c r="R48" s="89"/>
+      <c r="S48" s="90"/>
+      <c r="T48" s="61"/>
+      <c r="U48" s="61"/>
+      <c r="V48" s="61"/>
+      <c r="W48" s="61"/>
+      <c r="X48" s="61"/>
+      <c r="Y48" s="61"/>
+      <c r="Z48" s="61"/>
+      <c r="AA48" s="61"/>
+      <c r="AB48" s="61"/>
+      <c r="AC48" s="61"/>
+      <c r="AD48" s="61"/>
+      <c r="AE48" s="61"/>
+    </row>
+    <row r="49" customHeight="1" spans="1:31">
+      <c r="A49" s="60"/>
+      <c r="B49" s="15"/>
+      <c r="C49" s="77"/>
+      <c r="D49" s="77"/>
+      <c r="E49" s="77"/>
+      <c r="F49" s="77"/>
+      <c r="G49" s="77"/>
+      <c r="H49" s="77"/>
+      <c r="I49" s="77"/>
+      <c r="J49" s="77"/>
+      <c r="K49" s="77"/>
+      <c r="L49" s="84"/>
+      <c r="M49" s="84"/>
+      <c r="N49" s="84"/>
+      <c r="O49" s="84"/>
+      <c r="P49" s="84"/>
+      <c r="Q49" s="84"/>
+      <c r="R49" s="84"/>
+      <c r="S49" s="84"/>
+      <c r="T49" s="61"/>
+      <c r="U49" s="61"/>
+      <c r="V49" s="61"/>
+      <c r="W49" s="61"/>
+      <c r="X49" s="61"/>
+      <c r="Y49" s="61"/>
+      <c r="Z49" s="61"/>
+      <c r="AA49" s="61"/>
+      <c r="AB49" s="61"/>
+      <c r="AC49" s="61"/>
+      <c r="AD49" s="61"/>
+      <c r="AE49" s="61"/>
+    </row>
+    <row r="50" customHeight="1" spans="1:31">
+      <c r="A50" s="60"/>
+      <c r="B50" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="C50" s="83"/>
-      <c r="D50" s="83"/>
-      <c r="E50" s="84"/>
-      <c r="F50" s="84"/>
-      <c r="G50" s="84"/>
-      <c r="H50" s="84"/>
-      <c r="I50" s="84"/>
-      <c r="J50" s="84"/>
-      <c r="K50" s="84"/>
-      <c r="L50" s="84"/>
-      <c r="M50" s="84"/>
-      <c r="N50" s="84"/>
-      <c r="O50" s="84"/>
-      <c r="P50" s="84"/>
-      <c r="Q50" s="84"/>
-    </row>
-    <row r="51" customHeight="1" spans="1:17">
-      <c r="A51" s="13"/>
-      <c r="B51" s="79"/>
-      <c r="C51" s="83" t="s">
+      <c r="C50" s="81"/>
+      <c r="D50" s="81"/>
+      <c r="E50" s="81"/>
+      <c r="F50" s="81"/>
+      <c r="G50" s="81"/>
+      <c r="H50" s="81"/>
+      <c r="I50" s="81"/>
+      <c r="J50" s="81"/>
+      <c r="K50" s="81"/>
+      <c r="L50" s="81"/>
+      <c r="M50" s="81"/>
+      <c r="N50" s="81"/>
+      <c r="O50" s="81"/>
+      <c r="P50" s="81"/>
+      <c r="Q50" s="81"/>
+      <c r="R50" s="61"/>
+      <c r="S50" s="61"/>
+      <c r="T50" s="61"/>
+      <c r="U50" s="61"/>
+      <c r="V50" s="61"/>
+      <c r="W50" s="61"/>
+      <c r="X50" s="61"/>
+      <c r="Y50" s="61"/>
+      <c r="Z50" s="61"/>
+      <c r="AA50" s="61"/>
+      <c r="AB50" s="61"/>
+      <c r="AC50" s="61"/>
+      <c r="AD50" s="61"/>
+      <c r="AE50" s="61"/>
+    </row>
+    <row r="51" customHeight="1" spans="1:31">
+      <c r="A51" s="60"/>
+      <c r="B51" s="78"/>
+      <c r="C51" s="81" t="s">
         <v>101</v>
       </c>
-      <c r="D51" s="83"/>
-      <c r="E51" s="84"/>
-      <c r="F51" s="84"/>
-      <c r="G51" s="84"/>
-      <c r="H51" s="84"/>
-      <c r="I51" s="84"/>
-      <c r="J51" s="84"/>
-      <c r="K51" s="84"/>
-      <c r="L51" s="84"/>
-      <c r="M51" s="84"/>
-      <c r="N51" s="84"/>
-      <c r="O51" s="84"/>
-      <c r="P51" s="84"/>
-      <c r="Q51" s="84"/>
-    </row>
-    <row r="52" customHeight="1" spans="2:17">
-      <c r="B52" s="79"/>
-      <c r="C52" s="83" t="s">
+      <c r="D51" s="81"/>
+      <c r="E51" s="81"/>
+      <c r="F51" s="81"/>
+      <c r="G51" s="81"/>
+      <c r="H51" s="81"/>
+      <c r="I51" s="81"/>
+      <c r="J51" s="81"/>
+      <c r="K51" s="81"/>
+      <c r="L51" s="81"/>
+      <c r="M51" s="81"/>
+      <c r="N51" s="81"/>
+      <c r="O51" s="81"/>
+      <c r="P51" s="81"/>
+      <c r="Q51" s="81"/>
+      <c r="R51" s="61"/>
+      <c r="S51" s="61"/>
+      <c r="T51" s="61"/>
+      <c r="U51" s="61"/>
+      <c r="V51" s="61"/>
+      <c r="W51" s="61"/>
+      <c r="X51" s="61"/>
+      <c r="Y51" s="61"/>
+      <c r="Z51" s="61"/>
+      <c r="AA51" s="61"/>
+      <c r="AB51" s="61"/>
+      <c r="AC51" s="61"/>
+      <c r="AD51" s="61"/>
+      <c r="AE51" s="61"/>
+    </row>
+    <row r="52" customHeight="1" spans="1:31">
+      <c r="A52" s="61"/>
+      <c r="B52" s="78"/>
+      <c r="C52" s="81" t="s">
         <v>102</v>
       </c>
-      <c r="D52" s="83"/>
-      <c r="E52" s="84"/>
-      <c r="F52" s="84"/>
-      <c r="G52" s="84"/>
-      <c r="H52" s="84"/>
-      <c r="I52" s="84"/>
-      <c r="J52" s="84"/>
-      <c r="K52" s="84"/>
-      <c r="L52" s="84"/>
-      <c r="M52" s="84"/>
-      <c r="N52" s="84"/>
-      <c r="O52" s="84"/>
-      <c r="P52" s="84"/>
-      <c r="Q52" s="84"/>
-    </row>
-    <row r="53" customHeight="1" spans="2:17">
-      <c r="B53" s="79"/>
-      <c r="C53" s="83" t="s">
+      <c r="D52" s="81"/>
+      <c r="E52" s="81"/>
+      <c r="F52" s="81"/>
+      <c r="G52" s="81"/>
+      <c r="H52" s="81"/>
+      <c r="I52" s="81"/>
+      <c r="J52" s="81"/>
+      <c r="K52" s="81"/>
+      <c r="L52" s="81"/>
+      <c r="M52" s="81"/>
+      <c r="N52" s="81"/>
+      <c r="O52" s="81"/>
+      <c r="P52" s="81"/>
+      <c r="Q52" s="81"/>
+      <c r="R52" s="61"/>
+      <c r="S52" s="61"/>
+      <c r="T52" s="61"/>
+      <c r="U52" s="61"/>
+      <c r="V52" s="61"/>
+      <c r="W52" s="61"/>
+      <c r="X52" s="61"/>
+      <c r="Y52" s="61"/>
+      <c r="Z52" s="61"/>
+      <c r="AA52" s="61"/>
+      <c r="AB52" s="61"/>
+      <c r="AC52" s="61"/>
+      <c r="AD52" s="61"/>
+      <c r="AE52" s="61"/>
+    </row>
+    <row r="53" customHeight="1" spans="1:31">
+      <c r="A53" s="61"/>
+      <c r="B53" s="78"/>
+      <c r="C53" s="81" t="s">
         <v>103</v>
       </c>
-      <c r="D53" s="83"/>
-      <c r="E53" s="84"/>
-      <c r="F53" s="84"/>
-      <c r="G53" s="84"/>
-      <c r="H53" s="84"/>
-      <c r="I53" s="84"/>
-      <c r="J53" s="84"/>
-      <c r="K53" s="84"/>
-      <c r="L53" s="84"/>
-      <c r="M53" s="84"/>
-      <c r="N53" s="84"/>
-      <c r="O53" s="84"/>
-      <c r="P53" s="84"/>
-      <c r="Q53" s="84"/>
-    </row>
-    <row r="54" customHeight="1" spans="2:17">
-      <c r="B54" s="77"/>
-      <c r="C54" s="83" t="s">
+      <c r="D53" s="81"/>
+      <c r="E53" s="81"/>
+      <c r="F53" s="81"/>
+      <c r="G53" s="81"/>
+      <c r="H53" s="81"/>
+      <c r="I53" s="81"/>
+      <c r="J53" s="81"/>
+      <c r="K53" s="81"/>
+      <c r="L53" s="81"/>
+      <c r="M53" s="81"/>
+      <c r="N53" s="81"/>
+      <c r="O53" s="81"/>
+      <c r="P53" s="81"/>
+      <c r="Q53" s="81"/>
+      <c r="R53" s="61"/>
+      <c r="S53" s="61"/>
+      <c r="T53" s="61"/>
+      <c r="U53" s="61"/>
+      <c r="V53" s="61"/>
+      <c r="W53" s="61"/>
+      <c r="X53" s="61"/>
+      <c r="Y53" s="61"/>
+      <c r="Z53" s="61"/>
+      <c r="AA53" s="61"/>
+      <c r="AB53" s="61"/>
+      <c r="AC53" s="61"/>
+      <c r="AD53" s="61"/>
+      <c r="AE53" s="61"/>
+    </row>
+    <row r="54" customHeight="1" spans="1:31">
+      <c r="A54" s="61"/>
+      <c r="B54" s="76"/>
+      <c r="C54" s="81" t="s">
         <v>104</v>
       </c>
-      <c r="D54" s="83"/>
-      <c r="E54" s="84"/>
-      <c r="F54" s="84"/>
-      <c r="G54" s="84"/>
-      <c r="H54" s="84"/>
-      <c r="I54" s="84"/>
-      <c r="J54" s="84"/>
-      <c r="K54" s="84"/>
-      <c r="L54" s="84"/>
-      <c r="M54" s="84"/>
-      <c r="N54" s="84"/>
-      <c r="O54" s="84"/>
-      <c r="P54" s="84"/>
-      <c r="Q54" s="84"/>
-    </row>
-    <row r="55" customHeight="1" spans="2:17">
-      <c r="B55" s="84"/>
-      <c r="C55" s="83" t="s">
+      <c r="D54" s="81"/>
+      <c r="E54" s="81"/>
+      <c r="F54" s="81"/>
+      <c r="G54" s="81"/>
+      <c r="H54" s="81"/>
+      <c r="I54" s="81"/>
+      <c r="J54" s="81"/>
+      <c r="K54" s="81"/>
+      <c r="L54" s="81"/>
+      <c r="M54" s="81"/>
+      <c r="N54" s="81"/>
+      <c r="O54" s="81"/>
+      <c r="P54" s="81"/>
+      <c r="Q54" s="81"/>
+      <c r="R54" s="61"/>
+      <c r="S54" s="61"/>
+      <c r="T54" s="61"/>
+      <c r="U54" s="61"/>
+      <c r="V54" s="61"/>
+      <c r="W54" s="61"/>
+      <c r="X54" s="61"/>
+      <c r="Y54" s="61"/>
+      <c r="Z54" s="61"/>
+      <c r="AA54" s="61"/>
+      <c r="AB54" s="61"/>
+      <c r="AC54" s="61"/>
+      <c r="AD54" s="61"/>
+      <c r="AE54" s="61"/>
+    </row>
+    <row r="55" customHeight="1" spans="1:31">
+      <c r="A55" s="61"/>
+      <c r="B55" s="81"/>
+      <c r="C55" s="81" t="s">
         <v>105</v>
       </c>
-      <c r="D55" s="84"/>
-      <c r="E55" s="84"/>
-      <c r="F55" s="84"/>
-      <c r="G55" s="84"/>
-      <c r="H55" s="84"/>
-      <c r="I55" s="84"/>
-      <c r="J55" s="84"/>
-      <c r="K55" s="84"/>
-      <c r="L55" s="84"/>
-      <c r="M55" s="84"/>
-      <c r="N55" s="84"/>
-      <c r="O55" s="84"/>
-      <c r="P55" s="84"/>
-      <c r="Q55" s="84"/>
+      <c r="D55" s="81"/>
+      <c r="E55" s="81"/>
+      <c r="F55" s="81"/>
+      <c r="G55" s="81"/>
+      <c r="H55" s="81"/>
+      <c r="I55" s="81"/>
+      <c r="J55" s="81"/>
+      <c r="K55" s="81"/>
+      <c r="L55" s="81"/>
+      <c r="M55" s="81"/>
+      <c r="N55" s="81"/>
+      <c r="O55" s="81"/>
+      <c r="P55" s="81"/>
+      <c r="Q55" s="81"/>
+      <c r="R55" s="61"/>
+      <c r="S55" s="61"/>
+      <c r="T55" s="61"/>
+      <c r="U55" s="61"/>
+      <c r="V55" s="61"/>
+      <c r="W55" s="61"/>
+      <c r="X55" s="61"/>
+      <c r="Y55" s="61"/>
+      <c r="Z55" s="61"/>
+      <c r="AA55" s="61"/>
+      <c r="AB55" s="61"/>
+      <c r="AC55" s="61"/>
+      <c r="AD55" s="61"/>
+      <c r="AE55" s="61"/>
+    </row>
+    <row r="56" customHeight="1" spans="1:31">
+      <c r="A56" s="61"/>
+      <c r="B56" s="61"/>
+      <c r="C56" s="61"/>
+      <c r="D56" s="61"/>
+      <c r="E56" s="61"/>
+      <c r="F56" s="61"/>
+      <c r="G56" s="61"/>
+      <c r="H56" s="61"/>
+      <c r="I56" s="61"/>
+      <c r="J56" s="61"/>
+      <c r="K56" s="61"/>
+      <c r="L56" s="61"/>
+      <c r="M56" s="61"/>
+      <c r="N56" s="61"/>
+      <c r="O56" s="61"/>
+      <c r="P56" s="61"/>
+      <c r="Q56" s="61"/>
+      <c r="R56" s="61"/>
+      <c r="S56" s="61"/>
+      <c r="T56" s="61"/>
+      <c r="U56" s="61"/>
+      <c r="V56" s="61"/>
+      <c r="W56" s="61"/>
+      <c r="X56" s="61"/>
+      <c r="Y56" s="61"/>
+      <c r="Z56" s="61"/>
+      <c r="AA56" s="61"/>
+      <c r="AB56" s="61"/>
+      <c r="AC56" s="61"/>
+      <c r="AD56" s="61"/>
+      <c r="AE56" s="61"/>
+    </row>
+    <row r="57" customHeight="1" spans="1:31">
+      <c r="A57" s="61"/>
+      <c r="B57" s="61"/>
+      <c r="C57" s="61"/>
+      <c r="D57" s="61"/>
+      <c r="E57" s="61"/>
+      <c r="F57" s="61"/>
+      <c r="G57" s="61"/>
+      <c r="H57" s="61"/>
+      <c r="I57" s="61"/>
+      <c r="J57" s="61"/>
+      <c r="K57" s="61"/>
+      <c r="L57" s="61"/>
+      <c r="M57" s="61"/>
+      <c r="N57" s="61"/>
+      <c r="O57" s="61"/>
+      <c r="P57" s="61"/>
+      <c r="Q57" s="61"/>
+      <c r="R57" s="61"/>
+      <c r="S57" s="61"/>
+      <c r="T57" s="61"/>
+      <c r="U57" s="61"/>
+      <c r="V57" s="61"/>
+      <c r="W57" s="61"/>
+      <c r="X57" s="61"/>
+      <c r="Y57" s="61"/>
+      <c r="Z57" s="61"/>
+      <c r="AA57" s="61"/>
+      <c r="AB57" s="61"/>
+      <c r="AC57" s="61"/>
+      <c r="AD57" s="61"/>
+      <c r="AE57" s="61"/>
+    </row>
+    <row r="58" customHeight="1" spans="1:21">
+      <c r="A58" s="61"/>
+      <c r="B58" s="61"/>
+      <c r="C58" s="61"/>
+      <c r="D58" s="61"/>
+      <c r="E58" s="61"/>
+      <c r="F58" s="61"/>
+      <c r="G58" s="61"/>
+      <c r="H58" s="61"/>
+      <c r="I58" s="61"/>
+      <c r="J58" s="61"/>
+      <c r="K58" s="61"/>
+      <c r="L58" s="61"/>
+      <c r="M58" s="61"/>
+      <c r="N58" s="61"/>
+      <c r="O58" s="61"/>
+      <c r="P58" s="61"/>
+      <c r="Q58" s="61"/>
+      <c r="R58" s="61"/>
+      <c r="S58" s="61"/>
+      <c r="T58" s="61"/>
+      <c r="U58" s="61"/>
+    </row>
+    <row r="59" customHeight="1" spans="1:21">
+      <c r="A59" s="61"/>
+      <c r="B59" s="61"/>
+      <c r="C59" s="61"/>
+      <c r="D59" s="61"/>
+      <c r="E59" s="61"/>
+      <c r="F59" s="61"/>
+      <c r="G59" s="61"/>
+      <c r="H59" s="61"/>
+      <c r="I59" s="61"/>
+      <c r="J59" s="61"/>
+      <c r="K59" s="61"/>
+      <c r="L59" s="61"/>
+      <c r="M59" s="61"/>
+      <c r="N59" s="61"/>
+      <c r="O59" s="61"/>
+      <c r="P59" s="61"/>
+      <c r="Q59" s="61"/>
+      <c r="R59" s="61"/>
+      <c r="S59" s="61"/>
+      <c r="T59" s="61"/>
+      <c r="U59" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="60">
@@ -5362,7 +6446,7 @@
       </c>
       <c r="AJ1" s="23"/>
       <c r="AK1" s="23"/>
-      <c r="AL1" s="122" t="s">
+      <c r="AL1" s="115" t="s">
         <v>108</v>
       </c>
       <c r="AM1" s="23"/>
@@ -7402,7 +8486,7 @@
       </c>
       <c r="AJ1" s="23"/>
       <c r="AK1" s="23"/>
-      <c r="AL1" s="122" t="s">
+      <c r="AL1" s="115" t="s">
         <v>108</v>
       </c>
       <c r="AM1" s="23"/>
@@ -8564,7 +9648,7 @@
       </c>
       <c r="AJ1" s="23"/>
       <c r="AK1" s="23"/>
-      <c r="AL1" s="122" t="s">
+      <c r="AL1" s="115" t="s">
         <v>108</v>
       </c>
       <c r="AM1" s="23"/>
@@ -9093,7 +10177,7 @@
       </c>
       <c r="AJ1" s="23"/>
       <c r="AK1" s="23"/>
-      <c r="AL1" s="122" t="s">
+      <c r="AL1" s="115" t="s">
         <v>108</v>
       </c>
       <c r="AM1" s="23"/>
